--- a/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Fencing_Charge_and_Cost_25Oct2026.xlsx
+++ b/03_GC500_Delivery_Control/review_25Oct2026_baseplan7/GC500_Fencing_Charge_and_Cost_25Oct2026.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0#"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.00##"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.00##"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -101,19 +101,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -481,16 +478,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -504,14 +501,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>From the live record on 25 Oct 2026 (page v12.15), priced by the page itself: 167 signed red-book dockets. Our rates are the 2026 street card or your named rates. Advanced's costs are their approved pricing on the purchase orders for weeks 1-5 (115 dockets), and their rate sheet for week 6 and the event week (52 dockets) until their invoices land.</t>
+          <t>From the live record on 25 Oct 2026 (page v12.16), priced by the page itself: 167 signed red-book dockets, the fence under the scrim charged once. Our rates are the 2026 street card or your named rates. Advanced's costs are their approved pricing on the purchase orders for weeks 1-5 (115 dockets), and their rate sheet for week 6 and the event week (52 dockets) until their invoices land.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1. What we charge - how the $405,150.96 is built</t>
+          <t>1. What we charge the V8s, item by item</t>
         </is>
       </c>
     </row>
@@ -523,7 +520,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Qty (our dockets)</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -533,22 +530,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>We charge / unit</t>
+          <t>Rate we pay Advanced</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>Rate we charge V8s</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Total we charge</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>Our rate comes from</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>We charge</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>We pay / unit</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -560,11 +557,11 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Clean fence 1.8 m</t>
+          <t>Clean fence (not scrimmed)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>13270</v>
+        <v>9292.5</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -572,18 +569,18 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>16.1607</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="6" t="n">
+        <v>150173.23</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026 street card: Temporary Fencing 1.8m x 2.5m (per mtr)</t>
         </is>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>214452.46</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>10</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -606,18 +603,18 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>25.53</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="6" t="n">
+        <v>101545.7</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>your rate, 2026-09-24</t>
         </is>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>101545.7</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>24.4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -640,18 +637,18 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>13.08</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="6" t="n">
+        <v>66217.5</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026 street card: CCB Demarcation Fencing (per mtr) (confirmed 2026-09-24)</t>
         </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>66217.5</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>5.4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -674,18 +671,18 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>7.51</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="6" t="n">
+        <v>16484.48</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026 street card: Crowd Control Barrier (per mtr) (confirmed 2026-09-24)</t>
         </is>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>16484.48</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>5.4</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -708,18 +705,18 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>9.6511</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="6" t="n">
+        <v>2605.81</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026 street card: CCB Flat feet</t>
         </is>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>2605.81</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>5.4</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -742,18 +739,18 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="7" t="n">
         <v>142</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="6" t="n">
+        <v>1207</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>your rate, 2026-09-22</t>
         </is>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>1207</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>100</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -775,18 +772,18 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="7" t="n">
         <v>8.652000000000001</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="6" t="n">
+        <v>1189.65</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026 street card: Relocation of Fencing (per mtr)</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>1189.65</v>
-      </c>
-      <c r="G12" s="7" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>they bill relocation by the hour, $100</t>
@@ -808,18 +805,18 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="E13" s="7" t="n">
         <v>36.1839</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="6" t="n">
+        <v>796.04</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2026 street card: Pedestrian Gate</t>
         </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>796.04</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>61</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -841,18 +838,18 @@
           <t>each</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="7" t="n">
         <v>3.02</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="6" t="n">
+        <v>652.3200000000001</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026 street card: Fence Blocks( per block) (confirmed 2026-10-02)</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
-        <v>652.3200000000001</v>
-      </c>
-      <c r="G14" s="7" t="n"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>no per-block line on their sheet: the cost is on their invoice</t>
@@ -874,18 +871,18 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>included in the metre rate (the project manager, 1 Oct 2026)</t>
         </is>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>50</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -904,7 +901,7 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="9" t="n">
-        <v>405150.96</v>
+        <v>340871.73</v>
       </c>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -912,7 +909,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Each docket line is rounded to the cent, as the page and the build price it. Multiplying the totals above straight through gives 13 cents less ($405,150.83).</t>
+          <t>Clean fence is the papers' 13,270.0 m less the 3,977.5 m of fence under the scrim, which is charged once, in the scrim (v12.16). Each docket line is rounded to the cent, as the page prices it.</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
@@ -974,18 +971,18 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Clean fence 1.8 m</t>
+          <t>Clean fence (not scrimmed)</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>9718</v>
+        <v>9035.5</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -993,8 +990,8 @@
           <t>their clean metres leave out the scrimmed fence and the gate openings (see 5)</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
-        <v>97180</v>
+      <c r="F21" s="6" t="n">
+        <v>90355</v>
       </c>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
@@ -1013,11 +1010,11 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>24.4</v>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>89853</v>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1037,7 +1034,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>5.4</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1045,7 +1042,7 @@
           <t>on weeks 1-5 Advanced bill all CCB on this one line, same $5.40</t>
         </is>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="6" t="n">
         <v>34614</v>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1065,11 +1062,11 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="6" t="n">
         <v>5.4</v>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="6" t="n">
         <v>5008.5</v>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1089,11 +1086,11 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="6" t="n">
         <v>5.4</v>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="6" t="n">
         <v>664.2</v>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1113,11 +1110,11 @@
           <t>hr</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="6" t="n">
         <v>850</v>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1137,7 +1134,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1145,7 +1142,7 @@
           <t>relocation billed as labour hours</t>
         </is>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="6" t="n">
         <v>200</v>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1165,11 +1162,11 @@
           <t>each</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="6" t="n">
         <v>61</v>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="6" t="n">
         <v>1342</v>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1189,7 +1186,7 @@
           <t>each</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="6" t="n">
         <v>50</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1197,7 +1194,7 @@
           <t>billed by Advanced; not charged to the V8s (inside the metre rate)</t>
         </is>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="6" t="n">
         <v>10950</v>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1217,7 +1214,7 @@
           <t>each</t>
         </is>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1225,7 +1222,7 @@
           <t>on their week 3 invoice</t>
         </is>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="6" t="n">
         <v>300</v>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1242,7 +1239,7 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="10" t="n">
-        <v>240961.7</v>
+        <v>234136.7</v>
       </c>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
@@ -1261,7 +1258,7 @@
           <t>days</t>
         </is>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="6" t="n">
         <v>200</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1269,7 +1266,7 @@
           <t>on the purchase orders, weeks 1-5</t>
         </is>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="6" t="n">
         <v>9200</v>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1289,7 +1286,7 @@
           <t>rolls</t>
         </is>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="6" t="n">
         <v>64.5</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1297,7 +1294,7 @@
           <t>on purchase order 4647520</t>
         </is>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="6" t="n">
         <v>2580</v>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1317,7 +1314,7 @@
           <t>rolls</t>
         </is>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="6" t="n">
         <v>196</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1325,7 +1322,7 @@
           <t>on purchase order 4647520</t>
         </is>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="6" t="n">
         <v>784</v>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1342,11 +1339,11 @@
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>receipt 4918492 $8,992.00 against $10,869.00 at the sheet rates; the invoice stands (the project manager, 23 Oct)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>-1877</v>
+          <t>receipt 4918492 $8,992.00 against $10,144.00 at the sheet rates; the invoice stands (the project manager, 23 Oct)</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>-1152</v>
       </c>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
@@ -1365,7 +1362,7 @@
           <t>receipt 4922398 $33,670.00 against $35,045.50 at the sheet rates; the invoice stands (the project manager, 23 Oct)</t>
         </is>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="6" t="n">
         <v>-1375.5</v>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1382,7 +1379,7 @@
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="10" t="n">
-        <v>250273.2</v>
+        <v>244173.2</v>
       </c>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
@@ -1401,7 +1398,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1409,7 +1406,7 @@
           <t>42 service notes: Advanced's labour, a cost only (inside our metre rates)</t>
         </is>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="6" t="n">
         <v>10850</v>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1426,7 +1423,7 @@
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="10" t="n">
-        <v>261123.2</v>
+        <v>255023.2</v>
       </c>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="4" t="n"/>
@@ -1445,7 +1442,7 @@
           <t>INV 93920 - partial Collection (receipt 4922343); not in the page's fencing cost</t>
         </is>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="6" t="n">
         <v>195</v>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1462,7 +1459,7 @@
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="9" t="n">
-        <v>261318.2</v>
+        <v>255218.2</v>
       </c>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
@@ -1530,8 +1527,8 @@
           <t>4647508</t>
         </is>
       </c>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n">
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n">
         <v>8992</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1541,10 +1538,10 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>invoiced; no sheet to check line by line; the order stands; our 6 dockets at their rates come to $10,869.00, so the invoice is $1,877.00 less</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="n">
+          <t>invoiced; no sheet to check line by line; the order stands; our 6 dockets at their rates come to $10,144.00, so the invoice is $1,152.00 less</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="n">
         <v>8992</v>
       </c>
       <c r="H45" s="2" t="n"/>
@@ -1560,10 +1557,10 @@
           <t>4647509</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="6" t="n">
         <v>33670.5</v>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D46" s="6" t="n">
         <v>33670</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1576,7 +1573,7 @@
           <t>sheet $33,670.50, 50 cents over the order; the order stands; not on their sheet: docket 36524 ($1,375.00 at their rates)</t>
         </is>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="6" t="n">
         <v>33670</v>
       </c>
       <c r="H46" s="2" t="n"/>
@@ -1592,10 +1589,10 @@
           <t>4647517</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="6" t="n">
         <v>26695</v>
       </c>
-      <c r="D47" s="7" t="n">
+      <c r="D47" s="6" t="n">
         <v>26695</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1608,7 +1605,7 @@
           <t>Advanced's approved sheet = the order, to the cent</t>
         </is>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="6" t="n">
         <v>26695</v>
       </c>
       <c r="H47" s="2" t="n"/>
@@ -1624,10 +1621,10 @@
           <t>4647515</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="6" t="n">
         <v>50154</v>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="D48" s="6" t="n">
         <v>50154</v>
       </c>
       <c r="E48" s="2" t="n"/>
@@ -1636,7 +1633,7 @@
           <t>Advanced's approved sheet = the order, to the cent; their sheet prints the order as 464517</t>
         </is>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="6" t="n">
         <v>50154</v>
       </c>
       <c r="H48" s="2" t="n"/>
@@ -1652,10 +1649,10 @@
           <t>4647519</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="6" t="n">
         <v>28246.5</v>
       </c>
-      <c r="D49" s="7" t="n">
+      <c r="D49" s="6" t="n">
         <v>28246.5</v>
       </c>
       <c r="E49" s="2" t="n"/>
@@ -1664,7 +1661,7 @@
           <t>Advanced's approved sheet = the order, to the cent</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="6" t="n">
         <v>28246.5</v>
       </c>
       <c r="H49" s="2" t="n"/>
@@ -1680,10 +1677,10 @@
           <t>4647520</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="6" t="n">
         <v>66272</v>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D50" s="6" t="n">
         <v>66272</v>
       </c>
       <c r="E50" s="2" t="n"/>
@@ -1692,7 +1689,7 @@
           <t>Advanced's approved sheet = the order, to the cent; not on their sheet: labour note 24479 ($50.00)</t>
         </is>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="6" t="n">
         <v>66322</v>
       </c>
       <c r="H50" s="2" t="n"/>
@@ -1708,16 +1705,16 @@
           <t>4647522</t>
         </is>
       </c>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
       <c r="E51" s="2" t="n"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>nothing billed yet; 45 dockets and 11 labour notes on our record, at their rates</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n">
-        <v>47043.7</v>
+      <c r="G51" s="6" t="n">
+        <v>40943.7</v>
       </c>
       <c r="H51" s="2" t="n"/>
     </row>
@@ -1732,15 +1729,15 @@
           <t>4647523</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
       <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
           <t>nothing billed yet; no papers yet</t>
         </is>
       </c>
-      <c r="G52" s="7" t="n"/>
+      <c r="G52" s="6" t="n"/>
       <c r="H52" s="2" t="n"/>
     </row>
     <row r="53">
@@ -1754,8 +1751,8 @@
           <t>4658850</t>
         </is>
       </c>
-      <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n">
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n">
         <v>195</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1768,7 +1765,7 @@
           <t>INV 93920 - partial Collection; tied to no docket (the collection forms carry counts, no money); not in the page's fencing cost</t>
         </is>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="6" t="n">
         <v>195</v>
       </c>
       <c r="H53" s="2" t="n"/>
@@ -1785,7 +1782,7 @@
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="9" t="n">
-        <v>261318.2</v>
+        <v>255218.2</v>
       </c>
       <c r="H54" s="8" t="n"/>
     </row>
@@ -1813,8 +1810,8 @@
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="n"/>
-      <c r="F57" s="7" t="n">
-        <v>405150.96</v>
+      <c r="F57" s="6" t="n">
+        <v>340871.73</v>
       </c>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
@@ -1829,8 +1826,8 @@
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
-      <c r="F58" s="7" t="n">
-        <v>261318.2</v>
+      <c r="F58" s="6" t="n">
+        <v>255218.2</v>
       </c>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
@@ -1846,33 +1843,33 @@
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>35.5% of what we charge</t>
+          <t>25.1% of what we charge</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>143832.76</v>
+        <v>85653.53</v>
       </c>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>5. Needs your call - scrim fence charged twice?</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="n"/>
-      <c r="C61" s="11" t="n"/>
-      <c r="D61" s="11" t="n"/>
-      <c r="E61" s="11" t="n"/>
-      <c r="F61" s="11" t="n"/>
-      <c r="G61" s="11" t="n"/>
-      <c r="H61" s="11" t="n"/>
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>5. The scrim fence is charged once (Andrew, 25 Oct 2026: "we charge once")</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>The scrim rate ($25.53 a metre, set 24 Sep) is the fence with shade cloth on it: card fence $16.16 + card shade cloth $9.37. Advanced bill braced-for-scrim the same way, all in ($24.40, not $10 + $24.40).</t>
+          <t>The scrim rate ($25.53 a metre, set 24 Sep) is the fence with shade cloth on it: card fence $16.16 + card shade cloth $9.37. Advanced bill braced-for-scrim the same way, all in ($24.40).</t>
         </is>
       </c>
       <c r="B62" s="2" t="n"/>
@@ -1900,7 +1897,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Our record charges the paper's clean metres at $16.16 and the scrim metres again at $25.53, so the fence under the scrim is charged twice: 3,977.5 m x $16.1607 = $64,279.18.</t>
+          <t>Since v12.16 (live 25 Oct 14:18) each docket with scrim carries one more line: its scrim metres off the clean at $16.1607. That took $64,279.23 off the charge (was $405,150.96); on the paid side it took the event week's estimate down $6,100, the way Advanced bill it.</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -1914,7 +1911,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Baseplan keys them as separate metres (line 3 clean, line 6 fence with scrim + line 10 shade cloth), as the 2026 programme does, and 2025 billed "1.8 m fence with scrim" as its own all-in metre ($26.75, mesh $17.65).</t>
+          <t>Against Baseplan's $309,106.83 for 9990776, our signed dockets come to $340,871.73: Baseplan is short $31,764.90.</t>
         </is>
       </c>
       <c r="B65" s="2" t="n"/>
@@ -1925,52 +1922,52 @@
       <c r="G65" s="2" t="n"/>
       <c r="H65" s="2" t="n"/>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>If that is right: we charge $340,871.78, not $405,150.96; Baseplan is short $31,764.95, not $96,044.13; the margin is $79,553.58 (23.3%).</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n"/>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-      <c r="G66" s="2" t="n"/>
-      <c r="H66" s="2" t="n"/>
-    </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Nothing on the record or the page has been changed: it is your rate ruling.</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>6. Also worth knowing</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Pedestrian gates: we pay $61.00 each and charge the card's $36.18, so each one loses $24.82 (22 gates, $546.04 under).</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>6. Also worth knowing</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
-      <c r="G69" s="3" t="n"/>
-      <c r="H69" s="3" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle gates: Advanced bill $50 each (219, $10,950.00); we charge none on their own, as the project manager settled (inside the metre rate).</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Pedestrian gates: we pay $61.00 each and charge the card's $36.18, so each one loses $24.82 (22 gates, $546.04 under).</t>
+          <t>The event week (19-23 Oct, 45 dockets) is costed at Advanced's rate sheet until their invoice comes in (order 4647522 has no amount yet), so the paid side can still move.</t>
         </is>
       </c>
       <c r="B70" s="2" t="n"/>
@@ -1984,7 +1981,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Vehicle gates: Advanced bill $50 each (219, $10,950.00); we charge none on their own, as the project manager settled (inside the metre rate).</t>
+          <t>Not in these figures: the demob (removal is inside the metre rate; its papers are still to come) and the fence team's event labour under the C004 scope (3.15 Security &amp; Demarcation Fencing, 213 h at $91.14 = $19,412.82), which is a separate charge.</t>
         </is>
       </c>
       <c r="B71" s="2" t="n"/>
@@ -1994,34 +1991,6 @@
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
       <c r="H71" s="2" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>The event week (19-23 Oct, 45 dockets) is costed at Advanced's rate sheet until their invoice comes in (order 4647522 has no amount yet), so the paid side can still move.</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n"/>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Not in these figures: the demob (removal is inside the metre rate; its papers are still to come) and the fence team's event labour under the C004 scope (3.15 Security &amp; Demarcation Fencing, 213 h at $91.14 = $19,412.82), which is a separate charge.</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="n"/>
-      <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2136,22 +2105,22 @@
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="7" t="n">
-        <v>16148.09</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>10869</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>-1877</v>
-      </c>
-      <c r="J2" s="7" t="n">
+      <c r="E2" s="6" t="n">
+        <v>14976.44</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>10144</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>-1152</v>
+      </c>
+      <c r="J2" s="6" t="n">
         <v>8992</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -2159,7 +2128,7 @@
           <t>4647508</t>
         </is>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="L2" s="6" t="n">
         <v>8992</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -2185,22 +2154,22 @@
       <c r="D3" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E3" s="7" t="n">
-        <v>52939.53</v>
-      </c>
-      <c r="F3" s="7" t="n">
+      <c r="E3" s="6" t="n">
+        <v>44899.57</v>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>32620.5</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="6" t="n">
         <v>425</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="6" t="n">
         <v>-1375.5</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="J3" s="6" t="n">
         <v>33670</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -2208,7 +2177,7 @@
           <t>4647509</t>
         </is>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="L3" s="6" t="n">
         <v>33670</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -2234,22 +2203,22 @@
       <c r="D4" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <v>47656.3</v>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="E4" s="6" t="n">
+        <v>44989.78</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>24570</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="6" t="n">
         <v>1600</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="6" t="n">
         <v>525</v>
       </c>
-      <c r="I4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7" t="n">
+      <c r="I4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6" t="n">
         <v>26695</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2257,7 +2226,7 @@
           <t>4647517</t>
         </is>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="L4" s="6" t="n">
         <v>26695</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2283,22 +2252,22 @@
       <c r="D5" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E5" s="7" t="n">
-        <v>83881.22</v>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="E5" s="6" t="n">
+        <v>63518.73</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>47504</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="6" t="n">
         <v>650</v>
       </c>
-      <c r="I5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7" t="n">
+      <c r="I5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="n">
         <v>50154</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2306,7 +2275,7 @@
           <t>4647515</t>
         </is>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="L5" s="6" t="n">
         <v>50154</v>
       </c>
       <c r="M5" s="2" t="n"/>
@@ -2328,22 +2297,22 @@
       <c r="D6" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>40810.39</v>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="E6" s="6" t="n">
+        <v>33295.65</v>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>25396.5</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="6" t="n">
         <v>1600</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="6" t="n">
         <v>1250</v>
       </c>
-      <c r="I6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7" t="n">
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="n">
         <v>28246.5</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2351,7 +2320,7 @@
           <t>4647519</t>
         </is>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="L6" s="6" t="n">
         <v>28246.5</v>
       </c>
       <c r="M6" s="2" t="n"/>
@@ -2373,22 +2342,22 @@
       <c r="D7" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="E7" s="7" t="n">
-        <v>105705.12</v>
-      </c>
-      <c r="F7" s="7" t="n">
+      <c r="E7" s="6" t="n">
+        <v>91039.28</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>59658</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="6" t="n">
         <v>5364</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="6" t="n">
         <v>1300</v>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="7" t="n">
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="n">
         <v>66322</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2396,7 +2365,7 @@
           <t>4647520</t>
         </is>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" s="6" t="n">
         <v>66272</v>
       </c>
       <c r="M7" s="2" t="n"/>
@@ -2418,30 +2387,30 @@
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>58010.31</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>40343.7</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="7" t="n">
+      <c r="E8" s="6" t="n">
+        <v>48152.28</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>34243.7</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>6700</v>
       </c>
-      <c r="I8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>47043.7</v>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>40943.7</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>4647522</t>
         </is>
       </c>
-      <c r="L8" s="7" t="n"/>
+      <c r="L8" s="6" t="n"/>
       <c r="M8" s="2" t="n"/>
     </row>
     <row r="9">
@@ -2458,10 +2427,10 @@
         <v>115</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>405150.96</v>
+        <v>340871.73</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>240961.7</v>
+        <v>234136.7</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>12564</v>
@@ -2470,10 +2439,10 @@
         <v>10850</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-3252.5</v>
+        <v>-2527.5</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>261123.2</v>
+        <v>255023.2</v>
       </c>
       <c r="K9" s="8" t="n"/>
       <c r="L9" s="8" t="n"/>
@@ -2497,7 +2466,7 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="6" t="n">
         <v>195</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2505,7 +2474,7 @@
           <t>4658850</t>
         </is>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="6" t="n">
         <v>195</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -2524,14 +2493,14 @@
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="9" t="n">
-        <v>405150.96</v>
+        <v>340871.73</v>
       </c>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
       <c r="H11" s="8" t="n"/>
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="9" t="n">
-        <v>261318.2</v>
+        <v>255218.2</v>
       </c>
       <c r="K11" s="8" t="n"/>
       <c r="L11" s="8" t="n"/>
@@ -2697,7 +2666,7 @@
       </c>
       <c r="U1" s="4" t="inlineStr">
         <is>
-          <t>Scrim also in clean (m)</t>
+          <t>Fence under the scrim, off the clean (m)</t>
         </is>
       </c>
       <c r="V1" s="4" t="inlineStr">
@@ -2733,10 +2702,10 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
-      <c r="O2" s="7" t="n">
+      <c r="O2" s="6" t="n">
         <v>3757.36</v>
       </c>
-      <c r="P2" s="7" t="n">
+      <c r="P2" s="6" t="n">
         <v>2475</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -2787,10 +2756,10 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
-      <c r="O3" s="7" t="n">
+      <c r="O3" s="6" t="n">
         <v>3999.77</v>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="P3" s="6" t="n">
         <v>2475</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -2841,10 +2810,10 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
-      <c r="O4" s="7" t="n">
+      <c r="O4" s="6" t="n">
         <v>4161.38</v>
       </c>
-      <c r="P4" s="7" t="n">
+      <c r="P4" s="6" t="n">
         <v>2575</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2893,10 +2862,10 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
-      <c r="O5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7" t="n">
+      <c r="O5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2915,58 +2884,58 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>36504</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Week 6</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Helen Park, BSF compound</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="12" t="n"/>
-      <c r="O6" s="13" t="n">
-        <v>3022.58</v>
-      </c>
-      <c r="P6" s="13" t="n">
-        <v>2494</v>
-      </c>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="11" t="n"/>
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="12" t="n">
+        <v>1850.93</v>
+      </c>
+      <c r="P6" s="12" t="n">
+        <v>1769</v>
+      </c>
+      <c r="Q6" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R6" s="12" t="n"/>
-      <c r="S6" s="12" t="n"/>
-      <c r="T6" s="12" t="n"/>
-      <c r="U6" s="12" t="n">
+      <c r="R6" s="11" t="n"/>
+      <c r="S6" s="11" t="n"/>
+      <c r="T6" s="11" t="n"/>
+      <c r="U6" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="V6" s="12" t="inlineStr">
+      <c r="V6" s="11" t="inlineStr">
         <is>
           <t>week 6: no sheet</t>
         </is>
@@ -3005,10 +2974,10 @@
       <c r="N7" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="O7" s="7" t="n">
+      <c r="O7" s="6" t="n">
         <v>1207</v>
       </c>
-      <c r="P7" s="7" t="n">
+      <c r="P7" s="6" t="n">
         <v>850</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3059,10 +3028,10 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
-      <c r="O8" s="7" t="n">
+      <c r="O8" s="6" t="n">
         <v>1575.67</v>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="P8" s="6" t="n">
         <v>1075</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3087,64 +3056,64 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>36506</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>S18 C.2 construction zone</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="11" t="n">
         <v>132.5</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="13" t="n">
-        <v>2396.59</v>
-      </c>
-      <c r="P9" s="13" t="n">
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="12" t="n">
+        <v>2234.98</v>
+      </c>
+      <c r="P9" s="12" t="n">
         <v>1469</v>
       </c>
-      <c r="Q9" s="12" t="inlineStr">
+      <c r="Q9" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647509</t>
         </is>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="R9" s="11" t="n">
         <v>122.5</v>
       </c>
-      <c r="S9" s="12" t="n">
+      <c r="S9" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="T9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="12" t="n">
+      <c r="T9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="V9" s="12" t="inlineStr">
+      <c r="V9" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3183,10 +3152,10 @@
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
-      <c r="O10" s="7" t="n">
+      <c r="O10" s="6" t="n">
         <v>121.21</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="P10" s="6" t="n">
         <v>75</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3243,10 +3212,10 @@
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
-      <c r="O11" s="7" t="n">
+      <c r="O11" s="6" t="n">
         <v>323.21</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="P11" s="6" t="n">
         <v>200</v>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3305,10 +3274,10 @@
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
-      <c r="O12" s="7" t="n">
+      <c r="O12" s="6" t="n">
         <v>9405.17</v>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="P12" s="6" t="n">
         <v>6297</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3365,10 +3334,10 @@
       </c>
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="n"/>
-      <c r="O13" s="7" t="n">
+      <c r="O13" s="6" t="n">
         <v>432.6</v>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="P13" s="6" t="n">
         <v>50</v>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3425,10 +3394,10 @@
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
-      <c r="O14" s="7" t="n">
+      <c r="O14" s="6" t="n">
         <v>2787.72</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="P14" s="6" t="n">
         <v>1875</v>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3453,130 +3422,130 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>S07 C-Zone</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="11" t="n">
         <v>127.5</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="11" t="n">
         <v>12.5</v>
       </c>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
-      <c r="N15" s="12" t="n"/>
-      <c r="O15" s="13" t="n">
-        <v>2379.62</v>
-      </c>
-      <c r="P15" s="13" t="n">
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="11" t="n"/>
+      <c r="O15" s="12" t="n">
+        <v>2177.61</v>
+      </c>
+      <c r="P15" s="12" t="n">
         <v>1455</v>
       </c>
-      <c r="Q15" s="12" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647509</t>
         </is>
       </c>
-      <c r="R15" s="12" t="n">
+      <c r="R15" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="S15" s="12" t="n">
+      <c r="S15" s="11" t="n">
         <v>12.5</v>
       </c>
-      <c r="T15" s="12" t="n">
+      <c r="T15" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="U15" s="12" t="n">
+      <c r="U15" s="11" t="n">
         <v>12.5</v>
       </c>
-      <c r="V15" s="12" t="inlineStr">
+      <c r="V15" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>36514</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Event Operations — iEDM compound</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="11" t="n">
         <v>147.5</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n">
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="13" t="n">
-        <v>4206.98</v>
-      </c>
-      <c r="P16" s="13" t="n">
+      <c r="K16" s="11" t="n"/>
+      <c r="L16" s="11" t="n"/>
+      <c r="M16" s="11" t="n"/>
+      <c r="N16" s="11" t="n"/>
+      <c r="O16" s="12" t="n">
+        <v>3075.73</v>
+      </c>
+      <c r="P16" s="12" t="n">
         <v>2694</v>
       </c>
-      <c r="Q16" s="12" t="inlineStr">
+      <c r="Q16" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647509</t>
         </is>
       </c>
-      <c r="R16" s="12" t="n">
+      <c r="R16" s="11" t="n">
         <v>62.5</v>
       </c>
-      <c r="S16" s="12" t="n">
+      <c r="S16" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="T16" s="12" t="n">
+      <c r="T16" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="U16" s="12" t="n">
+      <c r="U16" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="V16" s="12" t="inlineStr">
+      <c r="V16" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3615,10 +3584,10 @@
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
-      <c r="O17" s="7" t="n">
+      <c r="O17" s="6" t="n">
         <v>450.6</v>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="P17" s="6" t="n">
         <v>324</v>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -3675,10 +3644,10 @@
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
-      <c r="O18" s="7" t="n">
+      <c r="O18" s="6" t="n">
         <v>1414.06</v>
       </c>
-      <c r="P18" s="7" t="n">
+      <c r="P18" s="6" t="n">
         <v>1075</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -3735,10 +3704,10 @@
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
-      <c r="O19" s="7" t="n">
+      <c r="O19" s="6" t="n">
         <v>1090.85</v>
       </c>
-      <c r="P19" s="7" t="n">
+      <c r="P19" s="6" t="n">
         <v>725</v>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -3763,190 +3732,190 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>36518</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>S.O.5 — grandstand, back of house</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="12" t="n"/>
-      <c r="O20" s="13" t="n">
-        <v>1140.05</v>
-      </c>
-      <c r="P20" s="13" t="n">
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="11" t="n"/>
+      <c r="L20" s="11" t="n"/>
+      <c r="M20" s="11" t="n"/>
+      <c r="N20" s="11" t="n"/>
+      <c r="O20" s="12" t="n">
+        <v>776.4299999999999</v>
+      </c>
+      <c r="P20" s="12" t="n">
         <v>724</v>
       </c>
-      <c r="Q20" s="12" t="inlineStr">
+      <c r="Q20" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647509</t>
         </is>
       </c>
-      <c r="R20" s="12" t="n">
+      <c r="R20" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" s="12" t="n">
+      <c r="S20" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="T20" s="12" t="n">
+      <c r="T20" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="U20" s="12" t="n">
+      <c r="U20" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="V20" s="12" t="inlineStr">
+      <c r="V20" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>36519</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Event operations — iEDM compound</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n">
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="13" t="n">
-        <v>1850.93</v>
-      </c>
-      <c r="P21" s="13" t="n">
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="12" t="n">
+        <v>679.28</v>
+      </c>
+      <c r="P21" s="12" t="n">
         <v>1044</v>
       </c>
-      <c r="Q21" s="12" t="inlineStr">
+      <c r="Q21" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647509</t>
         </is>
       </c>
-      <c r="R21" s="12" t="n">
+      <c r="R21" s="11" t="n">
         <v>-72.5</v>
       </c>
-      <c r="S21" s="12" t="n">
+      <c r="S21" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="T21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="12" t="n">
+      <c r="T21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="V21" s="12" t="inlineStr">
+      <c r="V21" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>36520</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Coates compound / ABD compound</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="11" t="n">
         <v>112.5</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="12" t="n"/>
-      <c r="O22" s="13" t="n">
-        <v>2839.28</v>
-      </c>
-      <c r="P22" s="13" t="n">
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="11" t="n"/>
+      <c r="N22" s="11" t="n"/>
+      <c r="O22" s="12" t="n">
+        <v>2192.85</v>
+      </c>
+      <c r="P22" s="12" t="n">
         <v>1801</v>
       </c>
-      <c r="Q22" s="12" t="inlineStr">
+      <c r="Q22" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647509</t>
         </is>
       </c>
-      <c r="R22" s="12" t="n">
+      <c r="R22" s="11" t="n">
         <v>62.5</v>
       </c>
-      <c r="S22" s="12" t="n">
+      <c r="S22" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="T22" s="12" t="n">
+      <c r="T22" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="U22" s="12" t="n">
+      <c r="U22" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="V22" s="12" t="inlineStr">
+      <c r="V22" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3985,10 +3954,10 @@
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="n"/>
-      <c r="O23" s="7" t="n">
+      <c r="O23" s="6" t="n">
         <v>444.42</v>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="P23" s="6" t="n">
         <v>275</v>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -4045,10 +4014,10 @@
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
-      <c r="O24" s="7" t="n">
+      <c r="O24" s="6" t="n">
         <v>2084.03</v>
       </c>
-      <c r="P24" s="7" t="n">
+      <c r="P24" s="6" t="n">
         <v>1498.5</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -4073,62 +4042,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>36523</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Helen Park — BSF compound</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n">
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="13" t="n">
-        <v>574.4299999999999</v>
-      </c>
-      <c r="P25" s="13" t="n">
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="11" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="O25" s="12" t="n">
+        <v>210.81</v>
+      </c>
+      <c r="P25" s="12" t="n">
         <v>324</v>
       </c>
-      <c r="Q25" s="12" t="inlineStr">
+      <c r="Q25" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647509</t>
         </is>
       </c>
-      <c r="R25" s="12" t="n">
+      <c r="R25" s="11" t="n">
         <v>-22.5</v>
       </c>
-      <c r="S25" s="12" t="n">
+      <c r="S25" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="T25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="12" t="n">
+      <c r="T25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="V25" s="12" t="inlineStr">
+      <c r="V25" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -4167,10 +4136,10 @@
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
-      <c r="O26" s="7" t="n">
+      <c r="O26" s="6" t="n">
         <v>2222.1</v>
       </c>
-      <c r="P26" s="7" t="n">
+      <c r="P26" s="6" t="n">
         <v>1375</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -4221,10 +4190,10 @@
       </c>
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
-      <c r="O27" s="7" t="n">
+      <c r="O27" s="6" t="n">
         <v>519.12</v>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="P27" s="6" t="n">
         <v>100</v>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -4281,10 +4250,10 @@
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
-      <c r="O28" s="7" t="n">
+      <c r="O28" s="6" t="n">
         <v>161.61</v>
       </c>
-      <c r="P28" s="7" t="n">
+      <c r="P28" s="6" t="n">
         <v>100</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4341,10 +4310,10 @@
       </c>
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
-      <c r="O29" s="7" t="n">
+      <c r="O29" s="6" t="n">
         <v>237.93</v>
       </c>
-      <c r="P29" s="7" t="n">
+      <c r="P29" s="6" t="n">
         <v>150</v>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4369,64 +4338,64 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>36529</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>P.B.03</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="F30" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="13" t="n">
-        <v>982.53</v>
-      </c>
-      <c r="P30" s="13" t="n">
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="11" t="n"/>
+      <c r="O30" s="12" t="n">
+        <v>820.92</v>
+      </c>
+      <c r="P30" s="12" t="n">
         <v>594</v>
       </c>
-      <c r="Q30" s="12" t="inlineStr">
+      <c r="Q30" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647509</t>
         </is>
       </c>
-      <c r="R30" s="12" t="n">
+      <c r="R30" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="S30" s="12" t="n">
+      <c r="S30" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="T30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="12" t="n">
+      <c r="T30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="V30" s="12" t="inlineStr">
+      <c r="V30" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -4467,10 +4436,10 @@
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
-      <c r="O31" s="7" t="n">
+      <c r="O31" s="6" t="n">
         <v>617.91</v>
       </c>
-      <c r="P31" s="7" t="n">
+      <c r="P31" s="6" t="n">
         <v>420</v>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4495,126 +4464,126 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Pit building paddock</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n">
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
-      <c r="O32" s="13" t="n">
-        <v>2680.65</v>
-      </c>
-      <c r="P32" s="13" t="n">
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n"/>
+      <c r="J32" s="11" t="n"/>
+      <c r="K32" s="11" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="11" t="n"/>
+      <c r="N32" s="11" t="n"/>
+      <c r="O32" s="12" t="n">
+        <v>983.78</v>
+      </c>
+      <c r="P32" s="12" t="n">
         <v>1512</v>
       </c>
-      <c r="Q32" s="12" t="inlineStr">
+      <c r="Q32" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647509</t>
         </is>
       </c>
-      <c r="R32" s="12" t="n">
+      <c r="R32" s="11" t="n">
         <v>-105</v>
       </c>
-      <c r="S32" s="12" t="n">
+      <c r="S32" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="T32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="12" t="n">
+      <c r="T32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="V32" s="12" t="inlineStr">
+      <c r="V32" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>36532</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>S10 compound</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="11" t="n">
         <v>132.5</v>
       </c>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="n"/>
-      <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="12" t="n"/>
-      <c r="O33" s="13" t="n">
-        <v>5806.83</v>
-      </c>
-      <c r="P33" s="13" t="n">
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="12" t="n">
+        <v>3665.54</v>
+      </c>
+      <c r="P33" s="12" t="n">
         <v>3458</v>
       </c>
-      <c r="Q33" s="12" t="inlineStr">
+      <c r="Q33" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647509</t>
         </is>
       </c>
-      <c r="R33" s="12" t="n">
+      <c r="R33" s="11" t="n">
         <v>12.5</v>
       </c>
-      <c r="S33" s="12" t="n">
+      <c r="S33" s="11" t="n">
         <v>132.5</v>
       </c>
-      <c r="T33" s="12" t="n">
+      <c r="T33" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="U33" s="12" t="n">
+      <c r="U33" s="11" t="n">
         <v>132.5</v>
       </c>
-      <c r="V33" s="12" t="inlineStr">
+      <c r="V33" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -4653,10 +4622,10 @@
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="n"/>
-      <c r="O34" s="7" t="n">
+      <c r="O34" s="6" t="n">
         <v>727.23</v>
       </c>
-      <c r="P34" s="7" t="n">
+      <c r="P34" s="6" t="n">
         <v>500</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4713,10 +4682,10 @@
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
       <c r="N35" s="2" t="n"/>
-      <c r="O35" s="7" t="n">
+      <c r="O35" s="6" t="n">
         <v>3073.8</v>
       </c>
-      <c r="P35" s="7" t="n">
+      <c r="P35" s="6" t="n">
         <v>1269</v>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4773,10 +4742,10 @@
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
-      <c r="O36" s="7" t="n">
+      <c r="O36" s="6" t="n">
         <v>392.4</v>
       </c>
-      <c r="P36" s="7" t="n">
+      <c r="P36" s="6" t="n">
         <v>162</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4833,10 +4802,10 @@
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="n"/>
-      <c r="O37" s="7" t="n">
+      <c r="O37" s="6" t="n">
         <v>2787.72</v>
       </c>
-      <c r="P37" s="7" t="n">
+      <c r="P37" s="6" t="n">
         <v>1775</v>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4893,10 +4862,10 @@
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
-      <c r="O38" s="7" t="n">
+      <c r="O38" s="6" t="n">
         <v>2787.72</v>
       </c>
-      <c r="P38" s="7" t="n">
+      <c r="P38" s="6" t="n">
         <v>1775</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4953,10 +4922,10 @@
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
-      <c r="O39" s="7" t="n">
+      <c r="O39" s="6" t="n">
         <v>525.22</v>
       </c>
-      <c r="P39" s="7" t="n">
+      <c r="P39" s="6" t="n">
         <v>325</v>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4981,62 +4950,62 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>36539</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Week 4</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Cypress Carpark</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n">
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="12" t="n"/>
-      <c r="M40" s="12" t="n"/>
-      <c r="N40" s="12" t="n"/>
-      <c r="O40" s="13" t="n">
-        <v>1021.2</v>
-      </c>
-      <c r="P40" s="13" t="n">
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="11" t="n"/>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="11" t="n"/>
+      <c r="N40" s="11" t="n"/>
+      <c r="O40" s="12" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="P40" s="12" t="n">
         <v>576</v>
       </c>
-      <c r="Q40" s="12" t="inlineStr">
+      <c r="Q40" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647517</t>
         </is>
       </c>
-      <c r="R40" s="12" t="n">
+      <c r="R40" s="11" t="n">
         <v>-40</v>
       </c>
-      <c r="S40" s="12" t="n">
+      <c r="S40" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="T40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="12" t="n">
+      <c r="T40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="V40" s="12" t="inlineStr">
+      <c r="V40" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5075,10 +5044,10 @@
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="n"/>
-      <c r="O41" s="7" t="n">
+      <c r="O41" s="6" t="n">
         <v>4839.6</v>
       </c>
-      <c r="P41" s="7" t="n">
+      <c r="P41" s="6" t="n">
         <v>1998</v>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5135,10 +5104,10 @@
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="n"/>
-      <c r="O42" s="7" t="n">
+      <c r="O42" s="6" t="n">
         <v>187.75</v>
       </c>
-      <c r="P42" s="7" t="n">
+      <c r="P42" s="6" t="n">
         <v>135</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5195,10 +5164,10 @@
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
       <c r="N43" s="2" t="n"/>
-      <c r="O43" s="7" t="n">
+      <c r="O43" s="6" t="n">
         <v>784.8</v>
       </c>
-      <c r="P43" s="7" t="n">
+      <c r="P43" s="6" t="n">
         <v>324</v>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5255,10 +5224,10 @@
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
       <c r="N44" s="2" t="n"/>
-      <c r="O44" s="7" t="n">
+      <c r="O44" s="6" t="n">
         <v>323.21</v>
       </c>
-      <c r="P44" s="7" t="n">
+      <c r="P44" s="6" t="n">
         <v>200</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5283,66 +5252,66 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>36544</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>Week 4</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>K01 kitchen compound fencing</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="F45" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="G45" s="12" t="n"/>
-      <c r="H45" s="12" t="n"/>
-      <c r="I45" s="12" t="n"/>
-      <c r="J45" s="12" t="n">
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K45" s="12" t="n"/>
-      <c r="L45" s="12" t="n"/>
-      <c r="M45" s="12" t="n"/>
-      <c r="N45" s="12" t="n"/>
-      <c r="O45" s="13" t="n">
-        <v>2224.95</v>
-      </c>
-      <c r="P45" s="13" t="n">
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="11" t="n"/>
+      <c r="M45" s="11" t="n"/>
+      <c r="N45" s="11" t="n"/>
+      <c r="O45" s="12" t="n">
+        <v>1376.51</v>
+      </c>
+      <c r="P45" s="12" t="n">
         <v>1342</v>
       </c>
-      <c r="Q45" s="12" t="inlineStr">
+      <c r="Q45" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647517</t>
         </is>
       </c>
-      <c r="R45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="12" t="n">
+      <c r="R45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="T45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="12" t="n">
+      <c r="T45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="V45" s="12" t="inlineStr">
+      <c r="V45" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5381,10 +5350,10 @@
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n"/>
       <c r="N46" s="2" t="n"/>
-      <c r="O46" s="7" t="n">
+      <c r="O46" s="6" t="n">
         <v>161.61</v>
       </c>
-      <c r="P46" s="7" t="n">
+      <c r="P46" s="6" t="n">
         <v>100</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5441,10 +5410,10 @@
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
       <c r="N47" s="2" t="n"/>
-      <c r="O47" s="7" t="n">
+      <c r="O47" s="6" t="n">
         <v>363.62</v>
       </c>
-      <c r="P47" s="7" t="n">
+      <c r="P47" s="6" t="n">
         <v>225</v>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5469,64 +5438,64 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>36547</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>Week 4</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>PB01 footings</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="F48" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="G48" s="12" t="n"/>
-      <c r="H48" s="12" t="n"/>
-      <c r="I48" s="12" t="n"/>
-      <c r="J48" s="12" t="n"/>
-      <c r="K48" s="12" t="n"/>
-      <c r="L48" s="12" t="n"/>
-      <c r="M48" s="12" t="n"/>
-      <c r="N48" s="12" t="n"/>
-      <c r="O48" s="13" t="n">
-        <v>3022.58</v>
-      </c>
-      <c r="P48" s="13" t="n">
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="11" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="11" t="n"/>
+      <c r="K48" s="11" t="n"/>
+      <c r="L48" s="11" t="n"/>
+      <c r="M48" s="11" t="n"/>
+      <c r="N48" s="11" t="n"/>
+      <c r="O48" s="12" t="n">
+        <v>1850.93</v>
+      </c>
+      <c r="P48" s="12" t="n">
         <v>1769</v>
       </c>
-      <c r="Q48" s="12" t="inlineStr">
+      <c r="Q48" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647517</t>
         </is>
       </c>
-      <c r="R48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="12" t="n">
+      <c r="R48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="T48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="12" t="n">
+      <c r="T48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="V48" s="12" t="inlineStr">
+      <c r="V48" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5565,10 +5534,10 @@
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="2" t="n"/>
       <c r="N49" s="2" t="n"/>
-      <c r="O49" s="7" t="n">
+      <c r="O49" s="6" t="n">
         <v>7676.33</v>
       </c>
-      <c r="P49" s="7" t="n">
+      <c r="P49" s="6" t="n">
         <v>4750</v>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5625,10 +5594,10 @@
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n"/>
       <c r="N50" s="2" t="n"/>
-      <c r="O50" s="7" t="n">
+      <c r="O50" s="6" t="n">
         <v>525.22</v>
       </c>
-      <c r="P50" s="7" t="n">
+      <c r="P50" s="6" t="n">
         <v>130</v>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5685,10 +5654,10 @@
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n"/>
       <c r="N51" s="2" t="n"/>
-      <c r="O51" s="7" t="n">
+      <c r="O51" s="6" t="n">
         <v>1010.04</v>
       </c>
-      <c r="P51" s="7" t="n">
+      <c r="P51" s="6" t="n">
         <v>625</v>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -5745,10 +5714,10 @@
       <c r="L52" s="2" t="n"/>
       <c r="M52" s="2" t="n"/>
       <c r="N52" s="2" t="n"/>
-      <c r="O52" s="7" t="n">
+      <c r="O52" s="6" t="n">
         <v>6670.8</v>
       </c>
-      <c r="P52" s="7" t="n">
+      <c r="P52" s="6" t="n">
         <v>2754</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -5805,10 +5774,10 @@
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n"/>
       <c r="N53" s="2" t="n"/>
-      <c r="O53" s="7" t="n">
+      <c r="O53" s="6" t="n">
         <v>404.02</v>
       </c>
-      <c r="P53" s="7" t="n">
+      <c r="P53" s="6" t="n">
         <v>300</v>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -5865,10 +5834,10 @@
       <c r="L54" s="2" t="n"/>
       <c r="M54" s="2" t="n"/>
       <c r="N54" s="2" t="n"/>
-      <c r="O54" s="7" t="n">
+      <c r="O54" s="6" t="n">
         <v>202.01</v>
       </c>
-      <c r="P54" s="7" t="n">
+      <c r="P54" s="6" t="n">
         <v>125</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -5925,10 +5894,10 @@
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n"/>
       <c r="N55" s="2" t="n"/>
-      <c r="O55" s="7" t="n">
+      <c r="O55" s="6" t="n">
         <v>4610.7</v>
       </c>
-      <c r="P55" s="7" t="n">
+      <c r="P55" s="6" t="n">
         <v>1903.5</v>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -5985,10 +5954,10 @@
       <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n"/>
       <c r="N56" s="2" t="n"/>
-      <c r="O56" s="7" t="n">
+      <c r="O56" s="6" t="n">
         <v>484.82</v>
       </c>
-      <c r="P56" s="7" t="n">
+      <c r="P56" s="6" t="n">
         <v>300</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6045,10 +6014,10 @@
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n"/>
       <c r="N57" s="2" t="n"/>
-      <c r="O57" s="7" t="n">
+      <c r="O57" s="6" t="n">
         <v>5264.7</v>
       </c>
-      <c r="P57" s="7" t="n">
+      <c r="P57" s="6" t="n">
         <v>2038.5</v>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6105,10 +6074,10 @@
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n"/>
       <c r="N58" s="2" t="n"/>
-      <c r="O58" s="7" t="n">
+      <c r="O58" s="6" t="n">
         <v>1616.07</v>
       </c>
-      <c r="P58" s="7" t="n">
+      <c r="P58" s="6" t="n">
         <v>1000</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6165,10 +6134,10 @@
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
       <c r="N59" s="2" t="n"/>
-      <c r="O59" s="7" t="n">
+      <c r="O59" s="6" t="n">
         <v>161.61</v>
       </c>
-      <c r="P59" s="7" t="n">
+      <c r="P59" s="6" t="n">
         <v>100</v>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6227,10 +6196,10 @@
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n"/>
       <c r="N60" s="2" t="n"/>
-      <c r="O60" s="7" t="n">
+      <c r="O60" s="6" t="n">
         <v>4749.59</v>
       </c>
-      <c r="P60" s="7" t="n">
+      <c r="P60" s="6" t="n">
         <v>2643.5</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -6255,68 +6224,68 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>36560</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>GC Hwy median strip (north)</t>
         </is>
       </c>
-      <c r="E61" s="12" t="n">
+      <c r="E61" s="11" t="n">
         <v>507.5</v>
       </c>
-      <c r="F61" s="12" t="n">
+      <c r="F61" s="11" t="n">
         <v>427.5</v>
       </c>
-      <c r="G61" s="12" t="n">
+      <c r="G61" s="11" t="n">
         <v>447.5</v>
       </c>
-      <c r="H61" s="12" t="n"/>
-      <c r="I61" s="12" t="n"/>
-      <c r="J61" s="12" t="n">
+      <c r="H61" s="11" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K61" s="12" t="n"/>
-      <c r="L61" s="12" t="n"/>
-      <c r="M61" s="12" t="n"/>
-      <c r="N61" s="12" t="n"/>
-      <c r="O61" s="13" t="n">
-        <v>25005.12</v>
-      </c>
-      <c r="P61" s="13" t="n">
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="11" t="n"/>
+      <c r="M61" s="11" t="n"/>
+      <c r="N61" s="11" t="n"/>
+      <c r="O61" s="12" t="n">
+        <v>18096.42</v>
+      </c>
+      <c r="P61" s="12" t="n">
         <v>13858.5</v>
       </c>
-      <c r="Q61" s="12" t="inlineStr">
+      <c r="Q61" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647515</t>
         </is>
       </c>
-      <c r="R61" s="12" t="n">
+      <c r="R61" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="S61" s="12" t="n">
+      <c r="S61" s="11" t="n">
         <v>427.5</v>
       </c>
-      <c r="T61" s="12" t="n">
+      <c r="T61" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="U61" s="12" t="n">
+      <c r="U61" s="11" t="n">
         <v>427.5</v>
       </c>
-      <c r="V61" s="12" t="inlineStr">
+      <c r="V61" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -6355,10 +6324,10 @@
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="2" t="n"/>
       <c r="N62" s="2" t="n"/>
-      <c r="O62" s="7" t="n">
+      <c r="O62" s="6" t="n">
         <v>2302.9</v>
       </c>
-      <c r="P62" s="7" t="n">
+      <c r="P62" s="6" t="n">
         <v>1575</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -6415,10 +6384,10 @@
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n"/>
       <c r="N63" s="2" t="n"/>
-      <c r="O63" s="7" t="n">
+      <c r="O63" s="6" t="n">
         <v>5292.63</v>
       </c>
-      <c r="P63" s="7" t="n">
+      <c r="P63" s="6" t="n">
         <v>3275</v>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -6475,10 +6444,10 @@
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
       <c r="N64" s="2" t="n"/>
-      <c r="O64" s="7" t="n">
+      <c r="O64" s="6" t="n">
         <v>1962</v>
       </c>
-      <c r="P64" s="7" t="n">
+      <c r="P64" s="6" t="n">
         <v>810</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -6503,64 +6472,64 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>36564</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>WC15 - rear fencing (toilets)</t>
         </is>
       </c>
-      <c r="E65" s="12" t="n">
+      <c r="E65" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="F65" s="12" t="n">
+      <c r="F65" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="G65" s="12" t="n"/>
-      <c r="H65" s="12" t="n"/>
-      <c r="I65" s="12" t="n"/>
-      <c r="J65" s="12" t="n"/>
-      <c r="K65" s="12" t="n"/>
-      <c r="L65" s="12" t="n"/>
-      <c r="M65" s="12" t="n"/>
-      <c r="N65" s="12" t="n"/>
-      <c r="O65" s="13" t="n">
-        <v>1667.63</v>
-      </c>
-      <c r="P65" s="13" t="n">
+      <c r="G65" s="11" t="n"/>
+      <c r="H65" s="11" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="11" t="n"/>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="11" t="n"/>
+      <c r="M65" s="11" t="n"/>
+      <c r="N65" s="11" t="n"/>
+      <c r="O65" s="12" t="n">
+        <v>1021.2</v>
+      </c>
+      <c r="P65" s="12" t="n">
         <v>976</v>
       </c>
-      <c r="Q65" s="12" t="inlineStr">
+      <c r="Q65" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647515</t>
         </is>
       </c>
-      <c r="R65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="12" t="n">
+      <c r="R65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="T65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="12" t="n">
+      <c r="T65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="V65" s="12" t="inlineStr">
+      <c r="V65" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -6599,10 +6568,10 @@
       <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n"/>
       <c r="N66" s="2" t="n"/>
-      <c r="O66" s="7" t="n">
+      <c r="O66" s="6" t="n">
         <v>404.02</v>
       </c>
-      <c r="P66" s="7" t="n">
+      <c r="P66" s="6" t="n">
         <v>250</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -6627,64 +6596,64 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>36566</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>Rear of pit building / rear of Puppet Theatre</t>
         </is>
       </c>
-      <c r="E67" s="12" t="n"/>
-      <c r="F67" s="12" t="n">
+      <c r="E67" s="11" t="n"/>
+      <c r="F67" s="11" t="n">
         <v>270</v>
       </c>
-      <c r="G67" s="12" t="n"/>
-      <c r="H67" s="12" t="n"/>
-      <c r="I67" s="12" t="n"/>
-      <c r="J67" s="12" t="n"/>
-      <c r="K67" s="12" t="n"/>
-      <c r="L67" s="12" t="n"/>
-      <c r="M67" s="12" t="n">
+      <c r="G67" s="11" t="n"/>
+      <c r="H67" s="11" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="11" t="n"/>
+      <c r="K67" s="11" t="n"/>
+      <c r="L67" s="11" t="n"/>
+      <c r="M67" s="11" t="n">
         <v>216</v>
       </c>
-      <c r="N67" s="12" t="n"/>
-      <c r="O67" s="13" t="n">
-        <v>7545.42</v>
-      </c>
-      <c r="P67" s="13" t="n">
+      <c r="N67" s="11" t="n"/>
+      <c r="O67" s="12" t="n">
+        <v>3182.03</v>
+      </c>
+      <c r="P67" s="12" t="n">
         <v>3888</v>
       </c>
-      <c r="Q67" s="12" t="inlineStr">
+      <c r="Q67" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647515</t>
         </is>
       </c>
-      <c r="R67" s="12" t="n">
+      <c r="R67" s="11" t="n">
         <v>-270</v>
       </c>
-      <c r="S67" s="12" t="n">
+      <c r="S67" s="11" t="n">
         <v>270</v>
       </c>
-      <c r="T67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" s="12" t="n">
+      <c r="T67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="11" t="n">
         <v>270</v>
       </c>
-      <c r="V67" s="12" t="inlineStr">
+      <c r="V67" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -6723,10 +6692,10 @@
       <c r="L68" s="2" t="n"/>
       <c r="M68" s="2" t="n"/>
       <c r="N68" s="2" t="n"/>
-      <c r="O68" s="7" t="n">
+      <c r="O68" s="6" t="n">
         <v>1614.65</v>
       </c>
-      <c r="P68" s="7" t="n">
+      <c r="P68" s="6" t="n">
         <v>1161</v>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -6751,192 +6720,192 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="inlineStr">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>36568</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="11" t="inlineStr">
         <is>
           <t>GC Hwy median strip (south)</t>
         </is>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="E69" s="11" t="n">
         <v>462.5</v>
       </c>
-      <c r="F69" s="12" t="n">
+      <c r="F69" s="11" t="n">
         <v>447.5</v>
       </c>
-      <c r="G69" s="12" t="n">
+      <c r="G69" s="11" t="n">
         <v>420</v>
       </c>
-      <c r="H69" s="12" t="n"/>
-      <c r="I69" s="12" t="n"/>
-      <c r="J69" s="12" t="n"/>
-      <c r="K69" s="12" t="n"/>
-      <c r="L69" s="12" t="n"/>
-      <c r="M69" s="12" t="n"/>
-      <c r="N69" s="12" t="n"/>
-      <c r="O69" s="13" t="n">
-        <v>24392.6</v>
-      </c>
-      <c r="P69" s="13" t="n">
+      <c r="H69" s="11" t="n"/>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="11" t="n"/>
+      <c r="K69" s="11" t="n"/>
+      <c r="L69" s="11" t="n"/>
+      <c r="M69" s="11" t="n"/>
+      <c r="N69" s="11" t="n"/>
+      <c r="O69" s="12" t="n">
+        <v>17160.69</v>
+      </c>
+      <c r="P69" s="12" t="n">
         <v>13487</v>
       </c>
-      <c r="Q69" s="12" t="inlineStr">
+      <c r="Q69" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647515</t>
         </is>
       </c>
-      <c r="R69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" s="12" t="n">
+      <c r="R69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="11" t="n">
         <v>447.5</v>
       </c>
-      <c r="T69" s="12" t="n">
+      <c r="T69" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="U69" s="12" t="n">
+      <c r="U69" s="11" t="n">
         <v>447.5</v>
       </c>
-      <c r="V69" s="12" t="inlineStr">
+      <c r="V69" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="12" t="inlineStr">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>36569</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D70" s="11" t="inlineStr">
         <is>
           <t>Event - ELEC</t>
         </is>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="E70" s="11" t="n">
         <v>82.5</v>
       </c>
-      <c r="F70" s="12" t="n">
+      <c r="F70" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="G70" s="12" t="n"/>
-      <c r="H70" s="12" t="n"/>
-      <c r="I70" s="12" t="n"/>
-      <c r="J70" s="12" t="n"/>
-      <c r="K70" s="12" t="n"/>
-      <c r="L70" s="12" t="n"/>
-      <c r="M70" s="12" t="n"/>
-      <c r="N70" s="12" t="n"/>
-      <c r="O70" s="13" t="n">
-        <v>2992.71</v>
-      </c>
-      <c r="P70" s="13" t="n">
+      <c r="G70" s="11" t="n"/>
+      <c r="H70" s="11" t="n"/>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="11" t="n"/>
+      <c r="K70" s="11" t="n"/>
+      <c r="L70" s="11" t="n"/>
+      <c r="M70" s="11" t="n"/>
+      <c r="N70" s="11" t="n"/>
+      <c r="O70" s="12" t="n">
+        <v>1942.26</v>
+      </c>
+      <c r="P70" s="12" t="n">
         <v>1811</v>
       </c>
-      <c r="Q70" s="12" t="inlineStr">
+      <c r="Q70" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647515</t>
         </is>
       </c>
-      <c r="R70" s="12" t="n">
+      <c r="R70" s="11" t="n">
         <v>12.5</v>
       </c>
-      <c r="S70" s="12" t="n">
+      <c r="S70" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="T70" s="12" t="n">
+      <c r="T70" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="U70" s="12" t="n">
+      <c r="U70" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="V70" s="12" t="inlineStr">
+      <c r="V70" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="inlineStr">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>36570</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C71" s="12" t="inlineStr">
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D71" s="11" t="inlineStr">
         <is>
           <t>Telstra COW</t>
         </is>
       </c>
-      <c r="E71" s="12" t="n"/>
-      <c r="F71" s="12" t="n">
+      <c r="E71" s="11" t="n"/>
+      <c r="F71" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G71" s="12" t="n"/>
-      <c r="H71" s="12" t="n"/>
-      <c r="I71" s="12" t="n"/>
-      <c r="J71" s="12" t="n"/>
-      <c r="K71" s="12" t="n"/>
-      <c r="L71" s="12" t="n"/>
-      <c r="M71" s="12" t="n"/>
-      <c r="N71" s="12" t="n"/>
-      <c r="O71" s="13" t="n">
-        <v>255.3</v>
-      </c>
-      <c r="P71" s="13" t="n">
+      <c r="G71" s="11" t="n"/>
+      <c r="H71" s="11" t="n"/>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="11" t="n"/>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="11" t="n"/>
+      <c r="M71" s="11" t="n"/>
+      <c r="N71" s="11" t="n"/>
+      <c r="O71" s="12" t="n">
+        <v>93.69</v>
+      </c>
+      <c r="P71" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="Q71" s="12" t="inlineStr">
+      <c r="Q71" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647515</t>
         </is>
       </c>
-      <c r="R71" s="12" t="n">
+      <c r="R71" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="S71" s="12" t="n">
+      <c r="S71" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="T71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" s="12" t="n">
+      <c r="T71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="V71" s="12" t="inlineStr">
+      <c r="V71" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -6975,10 +6944,10 @@
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="n"/>
       <c r="N72" s="2" t="n"/>
-      <c r="O72" s="7" t="n">
+      <c r="O72" s="6" t="n">
         <v>5454.24</v>
       </c>
-      <c r="P72" s="7" t="n">
+      <c r="P72" s="6" t="n">
         <v>3425</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -7035,10 +7004,10 @@
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n"/>
       <c r="N73" s="2" t="n"/>
-      <c r="O73" s="7" t="n">
+      <c r="O73" s="6" t="n">
         <v>242.41</v>
       </c>
-      <c r="P73" s="7" t="n">
+      <c r="P73" s="6" t="n">
         <v>200</v>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -7095,10 +7064,10 @@
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="n"/>
       <c r="N74" s="2" t="n"/>
-      <c r="O74" s="7" t="n">
+      <c r="O74" s="6" t="n">
         <v>1575.67</v>
       </c>
-      <c r="P74" s="7" t="n">
+      <c r="P74" s="6" t="n">
         <v>975</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -7123,64 +7092,64 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="12" t="inlineStr">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>36574</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C75" s="12" t="inlineStr">
+      <c r="C75" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D75" s="11" t="inlineStr">
         <is>
           <t>TV parking</t>
         </is>
       </c>
-      <c r="E75" s="12" t="n">
+      <c r="E75" s="11" t="n">
         <v>177.5</v>
       </c>
-      <c r="F75" s="12" t="n">
+      <c r="F75" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G75" s="12" t="n"/>
-      <c r="H75" s="12" t="n"/>
-      <c r="I75" s="12" t="n"/>
-      <c r="J75" s="12" t="n"/>
-      <c r="K75" s="12" t="n"/>
-      <c r="L75" s="12" t="n"/>
-      <c r="M75" s="12" t="n"/>
-      <c r="N75" s="12" t="n"/>
-      <c r="O75" s="13" t="n">
-        <v>3123.82</v>
-      </c>
-      <c r="P75" s="13" t="n">
+      <c r="G75" s="11" t="n"/>
+      <c r="H75" s="11" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="11" t="n"/>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="11" t="n"/>
+      <c r="M75" s="11" t="n"/>
+      <c r="N75" s="11" t="n"/>
+      <c r="O75" s="12" t="n">
+        <v>2962.21</v>
+      </c>
+      <c r="P75" s="12" t="n">
         <v>1969</v>
       </c>
-      <c r="Q75" s="12" t="inlineStr">
+      <c r="Q75" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R75" s="12" t="n">
+      <c r="R75" s="11" t="n">
         <v>162.5</v>
       </c>
-      <c r="S75" s="12" t="n">
+      <c r="S75" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="T75" s="12" t="n">
+      <c r="T75" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="U75" s="12" t="n">
+      <c r="U75" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="V75" s="12" t="inlineStr">
+      <c r="V75" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -7219,10 +7188,10 @@
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="n"/>
       <c r="N76" s="2" t="n"/>
-      <c r="O76" s="7" t="n">
+      <c r="O76" s="6" t="n">
         <v>2181.69</v>
       </c>
-      <c r="P76" s="7" t="n">
+      <c r="P76" s="6" t="n">
         <v>1500</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -7247,128 +7216,128 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="12" t="inlineStr">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>36576</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C77" s="12" t="inlineStr">
+      <c r="C77" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="11" t="inlineStr">
         <is>
           <t>S01 — toilet infill</t>
         </is>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="E77" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="F77" s="12" t="n">
+      <c r="F77" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="G77" s="12" t="n"/>
-      <c r="H77" s="12" t="n"/>
-      <c r="I77" s="12" t="n"/>
-      <c r="J77" s="12" t="n"/>
-      <c r="K77" s="12" t="n"/>
-      <c r="L77" s="12" t="n"/>
-      <c r="M77" s="12" t="n"/>
-      <c r="N77" s="12" t="n"/>
-      <c r="O77" s="13" t="n">
-        <v>104.23</v>
-      </c>
-      <c r="P77" s="13" t="n">
+      <c r="G77" s="11" t="n"/>
+      <c r="H77" s="11" t="n"/>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="11" t="n"/>
+      <c r="K77" s="11" t="n"/>
+      <c r="L77" s="11" t="n"/>
+      <c r="M77" s="11" t="n"/>
+      <c r="N77" s="11" t="n"/>
+      <c r="O77" s="12" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="P77" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="Q77" s="12" t="inlineStr">
+      <c r="Q77" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" s="12" t="n">
+      <c r="R77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="T77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" s="12" t="n">
+      <c r="T77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="V77" s="12" t="inlineStr">
+      <c r="V77" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="12" t="inlineStr">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>36577</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C78" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D78" s="11" t="inlineStr">
         <is>
           <t>Club 500 storage — perimeter fence</t>
         </is>
       </c>
-      <c r="E78" s="12" t="n">
+      <c r="E78" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F78" s="12" t="n">
+      <c r="F78" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G78" s="12" t="n"/>
-      <c r="H78" s="12" t="n"/>
-      <c r="I78" s="12" t="n"/>
-      <c r="J78" s="12" t="n"/>
-      <c r="K78" s="12" t="n"/>
-      <c r="L78" s="12" t="n"/>
-      <c r="M78" s="12" t="n"/>
-      <c r="N78" s="12" t="n"/>
-      <c r="O78" s="13" t="n">
-        <v>1123.07</v>
-      </c>
-      <c r="P78" s="13" t="n">
+      <c r="G78" s="11" t="n"/>
+      <c r="H78" s="11" t="n"/>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="11" t="n"/>
+      <c r="K78" s="11" t="n"/>
+      <c r="L78" s="11" t="n"/>
+      <c r="M78" s="11" t="n"/>
+      <c r="N78" s="11" t="n"/>
+      <c r="O78" s="12" t="n">
+        <v>719.05</v>
+      </c>
+      <c r="P78" s="12" t="n">
         <v>710</v>
       </c>
-      <c r="Q78" s="12" t="inlineStr">
+      <c r="Q78" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="12" t="n">
+      <c r="R78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="T78" s="12" t="n">
+      <c r="T78" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="U78" s="12" t="n">
+      <c r="U78" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="V78" s="12" t="inlineStr">
+      <c r="V78" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -7407,10 +7376,10 @@
       <c r="L79" s="2" t="n"/>
       <c r="M79" s="2" t="n"/>
       <c r="N79" s="2" t="n"/>
-      <c r="O79" s="7" t="n">
+      <c r="O79" s="6" t="n">
         <v>1212.05</v>
       </c>
-      <c r="P79" s="7" t="n">
+      <c r="P79" s="6" t="n">
         <v>750</v>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -7435,66 +7404,66 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="12" t="inlineStr">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>36579</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D80" s="11" t="inlineStr">
         <is>
           <t>Commodore Park</t>
         </is>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E80" s="11" t="n">
         <v>177.5</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F80" s="11" t="n">
         <v>122.5</v>
       </c>
-      <c r="G80" s="12" t="n"/>
-      <c r="H80" s="12" t="n"/>
-      <c r="I80" s="12" t="n"/>
-      <c r="J80" s="12" t="n">
+      <c r="G80" s="11" t="n"/>
+      <c r="H80" s="11" t="n"/>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="K80" s="12" t="n"/>
-      <c r="L80" s="12" t="n"/>
-      <c r="M80" s="12" t="n"/>
-      <c r="N80" s="12" t="n"/>
-      <c r="O80" s="13" t="n">
-        <v>6068.32</v>
-      </c>
-      <c r="P80" s="13" t="n">
+      <c r="K80" s="11" t="n"/>
+      <c r="L80" s="11" t="n"/>
+      <c r="M80" s="11" t="n"/>
+      <c r="N80" s="11" t="n"/>
+      <c r="O80" s="12" t="n">
+        <v>4088.63</v>
+      </c>
+      <c r="P80" s="12" t="n">
         <v>3861</v>
       </c>
-      <c r="Q80" s="12" t="inlineStr">
+      <c r="Q80" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R80" s="12" t="n">
+      <c r="R80" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="S80" s="12" t="n">
+      <c r="S80" s="11" t="n">
         <v>122.5</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T80" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U80" s="11" t="n">
         <v>122.5</v>
       </c>
-      <c r="V80" s="12" t="inlineStr">
+      <c r="V80" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -7533,10 +7502,10 @@
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="2" t="n"/>
       <c r="N81" s="2" t="n"/>
-      <c r="O81" s="7" t="n">
+      <c r="O81" s="6" t="n">
         <v>2424.1</v>
       </c>
-      <c r="P81" s="7" t="n">
+      <c r="P81" s="6" t="n">
         <v>1500</v>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -7561,62 +7530,62 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="12" t="inlineStr">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>36581</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D82" s="11" t="inlineStr">
         <is>
           <t>S04 — Corporate</t>
         </is>
       </c>
-      <c r="E82" s="12" t="n"/>
-      <c r="F82" s="12" t="n">
+      <c r="E82" s="11" t="n"/>
+      <c r="F82" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="G82" s="12" t="n"/>
-      <c r="H82" s="12" t="n"/>
-      <c r="I82" s="12" t="n"/>
-      <c r="J82" s="12" t="n"/>
-      <c r="K82" s="12" t="n"/>
-      <c r="L82" s="12" t="n"/>
-      <c r="M82" s="12" t="n"/>
-      <c r="N82" s="12" t="n"/>
-      <c r="O82" s="13" t="n">
-        <v>1850.93</v>
-      </c>
-      <c r="P82" s="13" t="n">
+      <c r="G82" s="11" t="n"/>
+      <c r="H82" s="11" t="n"/>
+      <c r="I82" s="11" t="n"/>
+      <c r="J82" s="11" t="n"/>
+      <c r="K82" s="11" t="n"/>
+      <c r="L82" s="11" t="n"/>
+      <c r="M82" s="11" t="n"/>
+      <c r="N82" s="11" t="n"/>
+      <c r="O82" s="12" t="n">
+        <v>679.28</v>
+      </c>
+      <c r="P82" s="12" t="n">
         <v>1044</v>
       </c>
-      <c r="Q82" s="12" t="inlineStr">
+      <c r="Q82" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R82" s="12" t="n">
+      <c r="R82" s="11" t="n">
         <v>-72.5</v>
       </c>
-      <c r="S82" s="12" t="n">
+      <c r="S82" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="T82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="12" t="n">
+      <c r="T82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="V82" s="12" t="inlineStr">
+      <c r="V82" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -7655,10 +7624,10 @@
       <c r="L83" s="2" t="n"/>
       <c r="M83" s="2" t="n"/>
       <c r="N83" s="2" t="n"/>
-      <c r="O83" s="7" t="n">
+      <c r="O83" s="6" t="n">
         <v>1333.26</v>
       </c>
-      <c r="P83" s="7" t="n">
+      <c r="P83" s="6" t="n">
         <v>875</v>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -7683,450 +7652,450 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="inlineStr">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>36583</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="D84" s="11" t="inlineStr">
         <is>
           <t>Helen Park C.2 + perimeter fence</t>
         </is>
       </c>
-      <c r="E84" s="12" t="n">
+      <c r="E84" s="11" t="n">
         <v>215</v>
       </c>
-      <c r="F84" s="12" t="n">
+      <c r="F84" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="G84" s="12" t="n"/>
-      <c r="H84" s="12" t="n"/>
-      <c r="I84" s="12" t="n"/>
-      <c r="J84" s="12" t="n"/>
-      <c r="K84" s="12" t="n"/>
-      <c r="L84" s="12" t="n"/>
-      <c r="M84" s="12" t="n"/>
-      <c r="N84" s="12" t="n"/>
-      <c r="O84" s="13" t="n">
-        <v>4878.7</v>
-      </c>
-      <c r="P84" s="13" t="n">
+      <c r="G84" s="11" t="n"/>
+      <c r="H84" s="11" t="n"/>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="11" t="n"/>
+      <c r="K84" s="11" t="n"/>
+      <c r="L84" s="11" t="n"/>
+      <c r="M84" s="11" t="n"/>
+      <c r="N84" s="11" t="n"/>
+      <c r="O84" s="12" t="n">
+        <v>3989.86</v>
+      </c>
+      <c r="P84" s="12" t="n">
         <v>3092</v>
       </c>
-      <c r="Q84" s="12" t="inlineStr">
+      <c r="Q84" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R84" s="12" t="n">
+      <c r="R84" s="11" t="n">
         <v>145</v>
       </c>
-      <c r="S84" s="12" t="n">
+      <c r="S84" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="T84" s="12" t="n">
+      <c r="T84" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="U84" s="12" t="n">
+      <c r="U84" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="V84" s="12" t="inlineStr">
+      <c r="V84" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="inlineStr">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>36584</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C85" s="12" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr">
         <is>
           <t>North S01 — Infill</t>
         </is>
       </c>
-      <c r="E85" s="12" t="n">
+      <c r="E85" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="F85" s="12" t="n">
+      <c r="F85" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="G85" s="12" t="n"/>
-      <c r="H85" s="12" t="n"/>
-      <c r="I85" s="12" t="n"/>
-      <c r="J85" s="12" t="n"/>
-      <c r="K85" s="12" t="n"/>
-      <c r="L85" s="12" t="n"/>
-      <c r="M85" s="12" t="n"/>
-      <c r="N85" s="12" t="n"/>
-      <c r="O85" s="13" t="n">
-        <v>312.69</v>
-      </c>
-      <c r="P85" s="13" t="n">
+      <c r="G85" s="11" t="n"/>
+      <c r="H85" s="11" t="n"/>
+      <c r="I85" s="11" t="n"/>
+      <c r="J85" s="11" t="n"/>
+      <c r="K85" s="11" t="n"/>
+      <c r="L85" s="11" t="n"/>
+      <c r="M85" s="11" t="n"/>
+      <c r="N85" s="11" t="n"/>
+      <c r="O85" s="12" t="n">
+        <v>191.48</v>
+      </c>
+      <c r="P85" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="Q85" s="12" t="inlineStr">
+      <c r="Q85" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" s="12" t="n">
+      <c r="R85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="T85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" s="12" t="n">
+      <c r="T85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="V85" s="12" t="inlineStr">
+      <c r="V85" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="12" t="inlineStr">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>36585</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C86" s="12" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="D86" s="11" t="inlineStr">
         <is>
           <t>Podium</t>
         </is>
       </c>
-      <c r="E86" s="12" t="n">
+      <c r="E86" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="F86" s="12" t="n">
+      <c r="F86" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="G86" s="12" t="n"/>
-      <c r="H86" s="12" t="n"/>
-      <c r="I86" s="12" t="n"/>
-      <c r="J86" s="12" t="n">
+      <c r="G86" s="11" t="n"/>
+      <c r="H86" s="11" t="n"/>
+      <c r="I86" s="11" t="n"/>
+      <c r="J86" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K86" s="12" t="n"/>
-      <c r="L86" s="12" t="n"/>
-      <c r="M86" s="12" t="n"/>
-      <c r="N86" s="12" t="n"/>
-      <c r="O86" s="13" t="n">
-        <v>1912.26</v>
-      </c>
-      <c r="P86" s="13" t="n">
+      <c r="K86" s="11" t="n"/>
+      <c r="L86" s="11" t="n"/>
+      <c r="M86" s="11" t="n"/>
+      <c r="N86" s="11" t="n"/>
+      <c r="O86" s="12" t="n">
+        <v>1185.03</v>
+      </c>
+      <c r="P86" s="12" t="n">
         <v>1159</v>
       </c>
-      <c r="Q86" s="12" t="inlineStr">
+      <c r="Q86" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" s="12" t="n">
+      <c r="R86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="T86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" s="12" t="n">
+      <c r="T86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="V86" s="12" t="inlineStr">
+      <c r="V86" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="12" t="inlineStr">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>36586</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C87" s="12" t="inlineStr">
+      <c r="C87" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr">
+      <c r="D87" s="11" t="inlineStr">
         <is>
           <t>Teams Area</t>
         </is>
       </c>
-      <c r="E87" s="12" t="n">
+      <c r="E87" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="F87" s="12" t="n">
+      <c r="F87" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G87" s="12" t="n"/>
-      <c r="H87" s="12" t="n"/>
-      <c r="I87" s="12" t="n"/>
-      <c r="J87" s="12" t="n"/>
-      <c r="K87" s="12" t="n"/>
-      <c r="L87" s="12" t="n"/>
-      <c r="M87" s="12" t="n"/>
-      <c r="N87" s="12" t="n"/>
-      <c r="O87" s="13" t="n">
-        <v>1042.27</v>
-      </c>
-      <c r="P87" s="13" t="n">
+      <c r="G87" s="11" t="n"/>
+      <c r="H87" s="11" t="n"/>
+      <c r="I87" s="11" t="n"/>
+      <c r="J87" s="11" t="n"/>
+      <c r="K87" s="11" t="n"/>
+      <c r="L87" s="11" t="n"/>
+      <c r="M87" s="11" t="n"/>
+      <c r="N87" s="11" t="n"/>
+      <c r="O87" s="12" t="n">
+        <v>638.25</v>
+      </c>
+      <c r="P87" s="12" t="n">
         <v>610</v>
       </c>
-      <c r="Q87" s="12" t="inlineStr">
+      <c r="Q87" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" s="12" t="n">
+      <c r="R87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="T87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" s="12" t="n">
+      <c r="T87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="V87" s="12" t="inlineStr">
+      <c r="V87" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="12" t="inlineStr">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>36587</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="C88" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D88" s="12" t="inlineStr">
+      <c r="D88" s="11" t="inlineStr">
         <is>
           <t>Event Operations — perimeter fence</t>
         </is>
       </c>
-      <c r="E88" s="12" t="n">
+      <c r="E88" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F88" s="12" t="n">
+      <c r="F88" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="G88" s="12" t="n"/>
-      <c r="H88" s="12" t="n"/>
-      <c r="I88" s="12" t="n"/>
-      <c r="J88" s="12" t="n"/>
-      <c r="K88" s="12" t="n"/>
-      <c r="L88" s="12" t="n"/>
-      <c r="M88" s="12" t="n"/>
-      <c r="N88" s="12" t="n"/>
-      <c r="O88" s="13" t="n">
-        <v>1059.25</v>
-      </c>
-      <c r="P88" s="13" t="n">
+      <c r="G88" s="11" t="n"/>
+      <c r="H88" s="11" t="n"/>
+      <c r="I88" s="11" t="n"/>
+      <c r="J88" s="11" t="n"/>
+      <c r="K88" s="11" t="n"/>
+      <c r="L88" s="11" t="n"/>
+      <c r="M88" s="11" t="n"/>
+      <c r="N88" s="11" t="n"/>
+      <c r="O88" s="12" t="n">
+        <v>695.63</v>
+      </c>
+      <c r="P88" s="12" t="n">
         <v>699</v>
       </c>
-      <c r="Q88" s="12" t="inlineStr">
+      <c r="Q88" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" s="12" t="n">
+      <c r="R88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="T88" s="12" t="n">
+      <c r="T88" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="U88" s="12" t="n">
+      <c r="U88" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="V88" s="12" t="inlineStr">
+      <c r="V88" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="12" t="inlineStr">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>36588</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C89" s="12" t="inlineStr">
+      <c r="C89" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
+      <c r="D89" s="11" t="inlineStr">
         <is>
           <t>Club 500 Toilets</t>
         </is>
       </c>
-      <c r="E89" s="12" t="n">
+      <c r="E89" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="F89" s="12" t="n">
+      <c r="F89" s="11" t="n">
         <v>62.5</v>
       </c>
-      <c r="G89" s="12" t="n"/>
-      <c r="H89" s="12" t="n"/>
-      <c r="I89" s="12" t="n"/>
-      <c r="J89" s="12" t="n"/>
-      <c r="K89" s="12" t="n"/>
-      <c r="L89" s="12" t="n"/>
-      <c r="M89" s="12" t="n"/>
-      <c r="N89" s="12" t="n"/>
-      <c r="O89" s="13" t="n">
-        <v>3130.9</v>
-      </c>
-      <c r="P89" s="13" t="n">
+      <c r="G89" s="11" t="n"/>
+      <c r="H89" s="11" t="n"/>
+      <c r="I89" s="11" t="n"/>
+      <c r="J89" s="11" t="n"/>
+      <c r="K89" s="11" t="n"/>
+      <c r="L89" s="11" t="n"/>
+      <c r="M89" s="11" t="n"/>
+      <c r="N89" s="11" t="n"/>
+      <c r="O89" s="12" t="n">
+        <v>2120.86</v>
+      </c>
+      <c r="P89" s="12" t="n">
         <v>1850</v>
       </c>
-      <c r="Q89" s="12" t="inlineStr">
+      <c r="Q89" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R89" s="12" t="n">
+      <c r="R89" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="S89" s="12" t="n">
+      <c r="S89" s="11" t="n">
         <v>62.5</v>
       </c>
-      <c r="T89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" s="12" t="n">
+      <c r="T89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" s="11" t="n">
         <v>62.5</v>
       </c>
-      <c r="V89" s="12" t="inlineStr">
+      <c r="V89" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="12" t="inlineStr">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>36589</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C90" s="12" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="D90" s="12" t="inlineStr">
+      <c r="D90" s="11" t="inlineStr">
         <is>
           <t>S04 Corporate Toilets</t>
         </is>
       </c>
-      <c r="E90" s="12" t="n">
+      <c r="E90" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="F90" s="12" t="n">
+      <c r="F90" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="G90" s="12" t="n"/>
-      <c r="H90" s="12" t="n"/>
-      <c r="I90" s="12" t="n"/>
-      <c r="J90" s="12" t="n"/>
-      <c r="K90" s="12" t="n"/>
-      <c r="L90" s="12" t="n"/>
-      <c r="M90" s="12" t="n"/>
-      <c r="N90" s="12" t="n"/>
-      <c r="O90" s="13" t="n">
-        <v>625.36</v>
-      </c>
-      <c r="P90" s="13" t="n">
+      <c r="G90" s="11" t="n"/>
+      <c r="H90" s="11" t="n"/>
+      <c r="I90" s="11" t="n"/>
+      <c r="J90" s="11" t="n"/>
+      <c r="K90" s="11" t="n"/>
+      <c r="L90" s="11" t="n"/>
+      <c r="M90" s="11" t="n"/>
+      <c r="N90" s="11" t="n"/>
+      <c r="O90" s="12" t="n">
+        <v>382.95</v>
+      </c>
+      <c r="P90" s="12" t="n">
         <v>366</v>
       </c>
-      <c r="Q90" s="12" t="inlineStr">
+      <c r="Q90" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647519</t>
         </is>
       </c>
-      <c r="R90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="12" t="n">
+      <c r="R90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="T90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="12" t="n">
+      <c r="T90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="V90" s="12" t="inlineStr">
+      <c r="V90" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -8165,10 +8134,10 @@
       <c r="L91" s="2" t="n"/>
       <c r="M91" s="2" t="n"/>
       <c r="N91" s="2" t="n"/>
-      <c r="O91" s="7" t="n">
+      <c r="O91" s="6" t="n">
         <v>1737.28</v>
       </c>
-      <c r="P91" s="7" t="n">
+      <c r="P91" s="6" t="n">
         <v>1175</v>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -8227,10 +8196,10 @@
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="2" t="n"/>
       <c r="N92" s="2" t="n"/>
-      <c r="O92" s="7" t="n">
+      <c r="O92" s="6" t="n">
         <v>1193.9</v>
       </c>
-      <c r="P92" s="7" t="n">
+      <c r="P92" s="6" t="n">
         <v>567</v>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -8287,10 +8256,10 @@
       <c r="L93" s="2" t="n"/>
       <c r="M93" s="2" t="n"/>
       <c r="N93" s="2" t="n"/>
-      <c r="O93" s="7" t="n">
+      <c r="O93" s="6" t="n">
         <v>2222.1</v>
       </c>
-      <c r="P93" s="7" t="n">
+      <c r="P93" s="6" t="n">
         <v>1375</v>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -8347,10 +8316,10 @@
       <c r="L94" s="2" t="n"/>
       <c r="M94" s="2" t="n"/>
       <c r="N94" s="2" t="n"/>
-      <c r="O94" s="7" t="n">
+      <c r="O94" s="6" t="n">
         <v>1454.46</v>
       </c>
-      <c r="P94" s="7" t="n">
+      <c r="P94" s="6" t="n">
         <v>900</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -8407,10 +8376,10 @@
       <c r="L95" s="2" t="n"/>
       <c r="M95" s="2" t="n"/>
       <c r="N95" s="2" t="n"/>
-      <c r="O95" s="7" t="n">
+      <c r="O95" s="6" t="n">
         <v>168.98</v>
       </c>
-      <c r="P95" s="7" t="n">
+      <c r="P95" s="6" t="n">
         <v>121.5</v>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -8467,10 +8436,10 @@
       <c r="L96" s="2" t="n"/>
       <c r="M96" s="2" t="n"/>
       <c r="N96" s="2" t="n"/>
-      <c r="O96" s="7" t="n">
+      <c r="O96" s="6" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="P96" s="7" t="n">
+      <c r="P96" s="6" t="n">
         <v>54</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -8531,10 +8500,10 @@
       <c r="L97" s="2" t="n"/>
       <c r="M97" s="2" t="n"/>
       <c r="N97" s="2" t="n"/>
-      <c r="O97" s="7" t="n">
+      <c r="O97" s="6" t="n">
         <v>10163.29</v>
       </c>
-      <c r="P97" s="7" t="n">
+      <c r="P97" s="6" t="n">
         <v>6007.5</v>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -8559,190 +8528,190 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="12" t="inlineStr">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>36597</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C98" s="12" t="inlineStr">
+      <c r="C98" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D98" s="12" t="inlineStr">
+      <c r="D98" s="11" t="inlineStr">
         <is>
           <t>The Spit - McMahon's/HTH Compound</t>
         </is>
       </c>
-      <c r="E98" s="12" t="n"/>
-      <c r="F98" s="12" t="n">
+      <c r="E98" s="11" t="n"/>
+      <c r="F98" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="G98" s="12" t="n"/>
-      <c r="H98" s="12" t="n"/>
-      <c r="I98" s="12" t="n"/>
-      <c r="J98" s="12" t="n"/>
-      <c r="K98" s="12" t="n"/>
-      <c r="L98" s="12" t="n"/>
-      <c r="M98" s="12" t="n"/>
-      <c r="N98" s="12" t="n"/>
-      <c r="O98" s="13" t="n">
-        <v>446.78</v>
-      </c>
-      <c r="P98" s="13" t="n">
+      <c r="G98" s="11" t="n"/>
+      <c r="H98" s="11" t="n"/>
+      <c r="I98" s="11" t="n"/>
+      <c r="J98" s="11" t="n"/>
+      <c r="K98" s="11" t="n"/>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="11" t="n"/>
+      <c r="N98" s="11" t="n"/>
+      <c r="O98" s="12" t="n">
+        <v>163.97</v>
+      </c>
+      <c r="P98" s="12" t="n">
         <v>252</v>
       </c>
-      <c r="Q98" s="12" t="inlineStr">
+      <c r="Q98" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R98" s="12" t="n">
+      <c r="R98" s="11" t="n">
         <v>-17.5</v>
       </c>
-      <c r="S98" s="12" t="n">
+      <c r="S98" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="T98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="12" t="n">
+      <c r="T98" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="V98" s="12" t="inlineStr">
+      <c r="V98" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="12" t="inlineStr">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>36598</t>
         </is>
       </c>
-      <c r="B99" s="12" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C99" s="12" t="inlineStr">
+      <c r="C99" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D99" s="12" t="inlineStr">
+      <c r="D99" s="11" t="inlineStr">
         <is>
           <t>Main Beach Pde - Rhapsody</t>
         </is>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="E99" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="F99" s="12" t="n">
+      <c r="F99" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="G99" s="12" t="n"/>
-      <c r="H99" s="12" t="n"/>
-      <c r="I99" s="12" t="n"/>
-      <c r="J99" s="12" t="n"/>
-      <c r="K99" s="12" t="n"/>
-      <c r="L99" s="12" t="n"/>
-      <c r="M99" s="12" t="n"/>
-      <c r="N99" s="12" t="n"/>
-      <c r="O99" s="13" t="n">
-        <v>312.69</v>
-      </c>
-      <c r="P99" s="13" t="n">
+      <c r="G99" s="11" t="n"/>
+      <c r="H99" s="11" t="n"/>
+      <c r="I99" s="11" t="n"/>
+      <c r="J99" s="11" t="n"/>
+      <c r="K99" s="11" t="n"/>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="11" t="n"/>
+      <c r="N99" s="11" t="n"/>
+      <c r="O99" s="12" t="n">
+        <v>191.48</v>
+      </c>
+      <c r="P99" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="Q99" s="12" t="inlineStr">
+      <c r="Q99" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" s="12" t="n">
+      <c r="R99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="T99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" s="12" t="n">
+      <c r="T99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="V99" s="12" t="inlineStr">
+      <c r="V99" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="12" t="inlineStr">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>36599</t>
         </is>
       </c>
-      <c r="B100" s="12" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C100" s="12" t="inlineStr">
+      <c r="C100" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D100" s="12" t="inlineStr">
+      <c r="D100" s="11" t="inlineStr">
         <is>
           <t>Supply Compound</t>
         </is>
       </c>
-      <c r="E100" s="12" t="n">
+      <c r="E100" s="11" t="n">
         <v>147.5</v>
       </c>
-      <c r="F100" s="12" t="n">
+      <c r="F100" s="11" t="n">
         <v>147.5</v>
       </c>
-      <c r="G100" s="12" t="n"/>
-      <c r="H100" s="12" t="n"/>
-      <c r="I100" s="12" t="n"/>
-      <c r="J100" s="12" t="n"/>
-      <c r="K100" s="12" t="n"/>
-      <c r="L100" s="12" t="n"/>
-      <c r="M100" s="12" t="n"/>
-      <c r="N100" s="12" t="n"/>
-      <c r="O100" s="13" t="n">
-        <v>6149.38</v>
-      </c>
-      <c r="P100" s="13" t="n">
+      <c r="G100" s="11" t="n"/>
+      <c r="H100" s="11" t="n"/>
+      <c r="I100" s="11" t="n"/>
+      <c r="J100" s="11" t="n"/>
+      <c r="K100" s="11" t="n"/>
+      <c r="L100" s="11" t="n"/>
+      <c r="M100" s="11" t="n"/>
+      <c r="N100" s="11" t="n"/>
+      <c r="O100" s="12" t="n">
+        <v>3765.68</v>
+      </c>
+      <c r="P100" s="12" t="n">
         <v>3599</v>
       </c>
-      <c r="Q100" s="12" t="inlineStr">
+      <c r="Q100" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" s="12" t="n">
+      <c r="R100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="11" t="n">
         <v>147.5</v>
       </c>
-      <c r="T100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" s="12" t="n">
+      <c r="T100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" s="11" t="n">
         <v>147.5</v>
       </c>
-      <c r="V100" s="12" t="inlineStr">
+      <c r="V100" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -8779,10 +8748,10 @@
       <c r="L101" s="2" t="n"/>
       <c r="M101" s="2" t="n"/>
       <c r="N101" s="2" t="n"/>
-      <c r="O101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="7" t="n">
+      <c r="O101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="6" t="n">
         <v>200</v>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -8807,196 +8776,196 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="12" t="inlineStr">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>36601</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C102" s="12" t="inlineStr">
+      <c r="C102" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D102" s="12" t="inlineStr">
+      <c r="D102" s="11" t="inlineStr">
         <is>
           <t>Commodore Park - Ticket Entry</t>
         </is>
       </c>
-      <c r="E102" s="12" t="n">
+      <c r="E102" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="F102" s="12" t="n">
+      <c r="F102" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G102" s="12" t="n"/>
-      <c r="H102" s="12" t="n"/>
-      <c r="I102" s="12" t="n"/>
-      <c r="J102" s="12" t="n"/>
-      <c r="K102" s="12" t="n"/>
-      <c r="L102" s="12" t="n"/>
-      <c r="M102" s="12" t="n"/>
-      <c r="N102" s="12" t="n"/>
-      <c r="O102" s="13" t="n">
-        <v>1042.27</v>
-      </c>
-      <c r="P102" s="13" t="n">
+      <c r="G102" s="11" t="n"/>
+      <c r="H102" s="11" t="n"/>
+      <c r="I102" s="11" t="n"/>
+      <c r="J102" s="11" t="n"/>
+      <c r="K102" s="11" t="n"/>
+      <c r="L102" s="11" t="n"/>
+      <c r="M102" s="11" t="n"/>
+      <c r="N102" s="11" t="n"/>
+      <c r="O102" s="12" t="n">
+        <v>638.25</v>
+      </c>
+      <c r="P102" s="12" t="n">
         <v>610</v>
       </c>
-      <c r="Q102" s="12" t="inlineStr">
+      <c r="Q102" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" s="12" t="n">
+      <c r="R102" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="T102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" s="12" t="n">
+      <c r="T102" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="V102" s="12" t="inlineStr">
+      <c r="V102" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="12" t="inlineStr">
+      <c r="A103" s="11" t="inlineStr">
         <is>
           <t>36602</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C103" s="12" t="inlineStr">
+      <c r="C103" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D103" s="12" t="inlineStr">
+      <c r="D103" s="11" t="inlineStr">
         <is>
           <t>COW - OPTUS</t>
         </is>
       </c>
-      <c r="E103" s="12" t="n">
+      <c r="E103" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="F103" s="12" t="n">
+      <c r="F103" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="G103" s="12" t="n"/>
-      <c r="H103" s="12" t="n"/>
-      <c r="I103" s="12" t="n"/>
-      <c r="J103" s="12" t="n"/>
-      <c r="K103" s="12" t="n"/>
-      <c r="L103" s="12" t="n"/>
-      <c r="M103" s="12" t="n"/>
-      <c r="N103" s="12" t="n"/>
-      <c r="O103" s="13" t="n">
-        <v>1876.08</v>
-      </c>
-      <c r="P103" s="13" t="n">
+      <c r="G103" s="11" t="n"/>
+      <c r="H103" s="11" t="n"/>
+      <c r="I103" s="11" t="n"/>
+      <c r="J103" s="11" t="n"/>
+      <c r="K103" s="11" t="n"/>
+      <c r="L103" s="11" t="n"/>
+      <c r="M103" s="11" t="n"/>
+      <c r="N103" s="11" t="n"/>
+      <c r="O103" s="12" t="n">
+        <v>1148.85</v>
+      </c>
+      <c r="P103" s="12" t="n">
         <v>1098</v>
       </c>
-      <c r="Q103" s="12" t="inlineStr">
+      <c r="Q103" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" s="12" t="n">
+      <c r="R103" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="T103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" s="12" t="n">
+      <c r="T103" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="V103" s="12" t="inlineStr">
+      <c r="V103" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="12" t="inlineStr">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>36603</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="C104" s="12" t="inlineStr">
+      <c r="C104" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D104" s="12" t="inlineStr">
+      <c r="D104" s="11" t="inlineStr">
         <is>
           <t>Eastern Residents &amp; Demarc - Cable St to Gate 8A - DL &amp; DR</t>
         </is>
       </c>
-      <c r="E104" s="12" t="n">
+      <c r="E104" s="11" t="n">
         <v>537.5</v>
       </c>
-      <c r="F104" s="12" t="n">
+      <c r="F104" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="G104" s="12" t="n">
+      <c r="G104" s="11" t="n">
         <v>672.5</v>
       </c>
-      <c r="H104" s="12" t="n"/>
-      <c r="I104" s="12" t="n"/>
-      <c r="J104" s="12" t="n">
+      <c r="H104" s="11" t="n"/>
+      <c r="I104" s="11" t="n"/>
+      <c r="J104" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K104" s="12" t="n"/>
-      <c r="L104" s="12" t="n"/>
-      <c r="M104" s="12" t="n"/>
-      <c r="N104" s="12" t="n"/>
-      <c r="O104" s="13" t="n">
-        <v>18967.75</v>
-      </c>
-      <c r="P104" s="13" t="n">
+      <c r="K104" s="11" t="n"/>
+      <c r="L104" s="11" t="n"/>
+      <c r="M104" s="11" t="n"/>
+      <c r="N104" s="11" t="n"/>
+      <c r="O104" s="12" t="n">
+        <v>18119.31</v>
+      </c>
+      <c r="P104" s="12" t="n">
         <v>10356.5</v>
       </c>
-      <c r="Q104" s="12" t="inlineStr">
+      <c r="Q104" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R104" s="12" t="n">
+      <c r="R104" s="11" t="n">
         <v>450</v>
       </c>
-      <c r="S104" s="12" t="n">
+      <c r="S104" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="T104" s="12" t="n">
+      <c r="T104" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="U104" s="12" t="n">
+      <c r="U104" s="11" t="n">
         <v>52.5</v>
       </c>
-      <c r="V104" s="12" t="inlineStr">
+      <c r="V104" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -9035,10 +9004,10 @@
       <c r="L105" s="2" t="n"/>
       <c r="M105" s="2" t="n"/>
       <c r="N105" s="2" t="n"/>
-      <c r="O105" s="7" t="n">
+      <c r="O105" s="6" t="n">
         <v>1013.37</v>
       </c>
-      <c r="P105" s="7" t="n">
+      <c r="P105" s="6" t="n">
         <v>567</v>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -9095,10 +9064,10 @@
       <c r="L106" s="2" t="n"/>
       <c r="M106" s="2" t="n"/>
       <c r="N106" s="2" t="n"/>
-      <c r="O106" s="7" t="n">
+      <c r="O106" s="6" t="n">
         <v>1535.27</v>
       </c>
-      <c r="P106" s="7" t="n">
+      <c r="P106" s="6" t="n">
         <v>950</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -9155,10 +9124,10 @@
       <c r="L107" s="2" t="n"/>
       <c r="M107" s="2" t="n"/>
       <c r="N107" s="2" t="n"/>
-      <c r="O107" s="7" t="n">
+      <c r="O107" s="6" t="n">
         <v>161.61</v>
       </c>
-      <c r="P107" s="7" t="n">
+      <c r="P107" s="6" t="n">
         <v>100</v>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -9215,10 +9184,10 @@
       <c r="L108" s="2" t="n"/>
       <c r="M108" s="2" t="n"/>
       <c r="N108" s="2" t="n"/>
-      <c r="O108" s="7" t="n">
+      <c r="O108" s="6" t="n">
         <v>767.63</v>
       </c>
-      <c r="P108" s="7" t="n">
+      <c r="P108" s="6" t="n">
         <v>475</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -9277,10 +9246,10 @@
       <c r="L109" s="2" t="n"/>
       <c r="M109" s="2" t="n"/>
       <c r="N109" s="2" t="n"/>
-      <c r="O109" s="7" t="n">
+      <c r="O109" s="6" t="n">
         <v>4416.78</v>
       </c>
-      <c r="P109" s="7" t="n">
+      <c r="P109" s="6" t="n">
         <v>2414.5</v>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -9305,64 +9274,64 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="12" t="inlineStr">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>36609</t>
         </is>
       </c>
-      <c r="B110" s="12" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C110" s="12" t="inlineStr">
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D110" s="12" t="inlineStr">
+      <c r="D110" s="11" t="inlineStr">
         <is>
           <t>Esplanade south of Meriton - Porsche Lounge CZ</t>
         </is>
       </c>
-      <c r="E110" s="12" t="n">
+      <c r="E110" s="11" t="n">
         <v>420</v>
       </c>
-      <c r="F110" s="12" t="n">
+      <c r="F110" s="11" t="n">
         <v>420</v>
       </c>
-      <c r="G110" s="12" t="n"/>
-      <c r="H110" s="12" t="n"/>
-      <c r="I110" s="12" t="n"/>
-      <c r="J110" s="12" t="n"/>
-      <c r="K110" s="12" t="n"/>
-      <c r="L110" s="12" t="n"/>
-      <c r="M110" s="12" t="n"/>
-      <c r="N110" s="12" t="n"/>
-      <c r="O110" s="13" t="n">
-        <v>17510.09</v>
-      </c>
-      <c r="P110" s="13" t="n">
+      <c r="G110" s="11" t="n"/>
+      <c r="H110" s="11" t="n"/>
+      <c r="I110" s="11" t="n"/>
+      <c r="J110" s="11" t="n"/>
+      <c r="K110" s="11" t="n"/>
+      <c r="L110" s="11" t="n"/>
+      <c r="M110" s="11" t="n"/>
+      <c r="N110" s="11" t="n"/>
+      <c r="O110" s="12" t="n">
+        <v>10722.6</v>
+      </c>
+      <c r="P110" s="12" t="n">
         <v>6100</v>
       </c>
-      <c r="Q110" s="12" t="inlineStr">
+      <c r="Q110" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R110" s="12" t="n">
+      <c r="R110" s="11" t="n">
         <v>285</v>
       </c>
-      <c r="S110" s="12" t="n">
+      <c r="S110" s="11" t="n">
         <v>125</v>
       </c>
-      <c r="T110" s="12" t="n">
+      <c r="T110" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="U110" s="12" t="n">
+      <c r="U110" s="11" t="n">
         <v>420</v>
       </c>
-      <c r="V110" s="12" t="inlineStr">
+      <c r="V110" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -9405,10 +9374,10 @@
       <c r="L111" s="2" t="n"/>
       <c r="M111" s="2" t="n"/>
       <c r="N111" s="2" t="n"/>
-      <c r="O111" s="7" t="n">
+      <c r="O111" s="6" t="n">
         <v>8627.43</v>
       </c>
-      <c r="P111" s="7" t="n">
+      <c r="P111" s="6" t="n">
         <v>5077</v>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -9433,66 +9402,66 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="12" t="inlineStr">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t>36611</t>
         </is>
       </c>
-      <c r="B112" s="12" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C112" s="12" t="inlineStr">
+      <c r="C112" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D112" s="12" t="inlineStr">
+      <c r="D112" s="11" t="inlineStr">
         <is>
           <t>Surfers Paradise Light Rail</t>
         </is>
       </c>
-      <c r="E112" s="12" t="n">
+      <c r="E112" s="11" t="n">
         <v>165</v>
       </c>
-      <c r="F112" s="12" t="n">
+      <c r="F112" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="G112" s="12" t="n"/>
-      <c r="H112" s="12" t="n">
+      <c r="G112" s="11" t="n"/>
+      <c r="H112" s="11" t="n">
         <v>130</v>
       </c>
-      <c r="I112" s="12" t="n"/>
-      <c r="J112" s="12" t="n"/>
-      <c r="K112" s="12" t="n"/>
-      <c r="L112" s="12" t="n"/>
-      <c r="M112" s="12" t="n"/>
-      <c r="N112" s="12" t="n"/>
-      <c r="O112" s="13" t="n">
-        <v>4408.72</v>
-      </c>
-      <c r="P112" s="13" t="n">
+      <c r="I112" s="11" t="n"/>
+      <c r="J112" s="11" t="n"/>
+      <c r="K112" s="11" t="n"/>
+      <c r="L112" s="11" t="n"/>
+      <c r="M112" s="11" t="n"/>
+      <c r="N112" s="11" t="n"/>
+      <c r="O112" s="12" t="n">
+        <v>3923.9</v>
+      </c>
+      <c r="P112" s="12" t="n">
         <v>2884</v>
       </c>
-      <c r="Q112" s="12" t="inlineStr">
+      <c r="Q112" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R112" s="12" t="n">
+      <c r="R112" s="11" t="n">
         <v>125</v>
       </c>
-      <c r="S112" s="12" t="n">
+      <c r="S112" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="T112" s="12" t="n">
+      <c r="T112" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="U112" s="12" t="n">
+      <c r="U112" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="V112" s="12" t="inlineStr">
+      <c r="V112" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -9533,10 +9502,10 @@
       <c r="L113" s="2" t="n"/>
       <c r="M113" s="2" t="n"/>
       <c r="N113" s="2" t="n"/>
-      <c r="O113" s="7" t="n">
+      <c r="O113" s="6" t="n">
         <v>5199.17</v>
       </c>
-      <c r="P113" s="7" t="n">
+      <c r="P113" s="6" t="n">
         <v>3733</v>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -9593,10 +9562,10 @@
       <c r="L114" s="2" t="n"/>
       <c r="M114" s="2" t="n"/>
       <c r="N114" s="2" t="n"/>
-      <c r="O114" s="7" t="n">
+      <c r="O114" s="6" t="n">
         <v>525.7</v>
       </c>
-      <c r="P114" s="7" t="n">
+      <c r="P114" s="6" t="n">
         <v>378</v>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -9621,128 +9590,128 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="12" t="inlineStr">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t>36614</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C115" s="12" t="inlineStr">
+      <c r="C115" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D115" s="12" t="inlineStr">
+      <c r="D115" s="11" t="inlineStr">
         <is>
           <t>S.0.8 B.O.H.</t>
         </is>
       </c>
-      <c r="E115" s="12" t="n">
+      <c r="E115" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="F115" s="12" t="n">
+      <c r="F115" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="G115" s="12" t="n"/>
-      <c r="H115" s="12" t="n"/>
-      <c r="I115" s="12" t="n"/>
-      <c r="J115" s="12" t="n"/>
-      <c r="K115" s="12" t="n"/>
-      <c r="L115" s="12" t="n"/>
-      <c r="M115" s="12" t="n"/>
-      <c r="N115" s="12" t="n"/>
-      <c r="O115" s="13" t="n">
-        <v>2816.48</v>
-      </c>
-      <c r="P115" s="13" t="n">
+      <c r="G115" s="11" t="n"/>
+      <c r="H115" s="11" t="n"/>
+      <c r="I115" s="11" t="n"/>
+      <c r="J115" s="11" t="n"/>
+      <c r="K115" s="11" t="n"/>
+      <c r="L115" s="11" t="n"/>
+      <c r="M115" s="11" t="n"/>
+      <c r="N115" s="11" t="n"/>
+      <c r="O115" s="12" t="n">
+        <v>1442.82</v>
+      </c>
+      <c r="P115" s="12" t="n">
         <v>1674</v>
       </c>
-      <c r="Q115" s="12" t="inlineStr">
+      <c r="Q115" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R115" s="12" t="n">
+      <c r="R115" s="11" t="n">
         <v>-50</v>
       </c>
-      <c r="S115" s="12" t="n">
+      <c r="S115" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="T115" s="12" t="n">
+      <c r="T115" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="U115" s="12" t="n">
+      <c r="U115" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="V115" s="12" t="inlineStr">
+      <c r="V115" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="12" t="inlineStr">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>36615</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C116" s="12" t="inlineStr">
+      <c r="C116" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D116" s="12" t="inlineStr">
+      <c r="D116" s="11" t="inlineStr">
         <is>
           <t>Gate 5 Compound</t>
         </is>
       </c>
-      <c r="E116" s="12" t="n">
+      <c r="E116" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="F116" s="12" t="n">
+      <c r="F116" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="G116" s="12" t="n"/>
-      <c r="H116" s="12" t="n"/>
-      <c r="I116" s="12" t="n"/>
-      <c r="J116" s="12" t="n"/>
-      <c r="K116" s="12" t="n"/>
-      <c r="L116" s="12" t="n"/>
-      <c r="M116" s="12" t="n"/>
-      <c r="N116" s="12" t="n"/>
-      <c r="O116" s="13" t="n">
-        <v>2798.88</v>
-      </c>
-      <c r="P116" s="13" t="n">
+      <c r="G116" s="11" t="n"/>
+      <c r="H116" s="11" t="n"/>
+      <c r="I116" s="11" t="n"/>
+      <c r="J116" s="11" t="n"/>
+      <c r="K116" s="11" t="n"/>
+      <c r="L116" s="11" t="n"/>
+      <c r="M116" s="11" t="n"/>
+      <c r="N116" s="11" t="n"/>
+      <c r="O116" s="12" t="n">
+        <v>2152.45</v>
+      </c>
+      <c r="P116" s="12" t="n">
         <v>1676</v>
       </c>
-      <c r="Q116" s="12" t="inlineStr">
+      <c r="Q116" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R116" s="12" t="n">
+      <c r="R116" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="S116" s="12" t="n">
+      <c r="S116" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="T116" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" s="12" t="n">
+      <c r="T116" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="V116" s="12" t="inlineStr">
+      <c r="V116" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -9781,10 +9750,10 @@
       <c r="L117" s="2" t="n"/>
       <c r="M117" s="2" t="n"/>
       <c r="N117" s="2" t="n"/>
-      <c r="O117" s="7" t="n">
+      <c r="O117" s="6" t="n">
         <v>2383.7</v>
       </c>
-      <c r="P117" s="7" t="n">
+      <c r="P117" s="6" t="n">
         <v>1525</v>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -9809,64 +9778,64 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="12" t="inlineStr">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>36617</t>
         </is>
       </c>
-      <c r="B118" s="12" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C118" s="12" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="D118" s="12" t="inlineStr">
+      <c r="D118" s="11" t="inlineStr">
         <is>
           <t>Main Beach Light Rail</t>
         </is>
       </c>
-      <c r="E118" s="12" t="n">
+      <c r="E118" s="11" t="n">
         <v>155</v>
       </c>
-      <c r="F118" s="12" t="n">
+      <c r="F118" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="G118" s="12" t="n"/>
-      <c r="H118" s="12" t="n"/>
-      <c r="I118" s="12" t="n"/>
-      <c r="J118" s="12" t="n"/>
-      <c r="K118" s="12" t="n"/>
-      <c r="L118" s="12" t="n"/>
-      <c r="M118" s="12" t="n"/>
-      <c r="N118" s="12" t="n"/>
-      <c r="O118" s="13" t="n">
-        <v>3462.29</v>
-      </c>
-      <c r="P118" s="13" t="n">
+      <c r="G118" s="11" t="n"/>
+      <c r="H118" s="11" t="n"/>
+      <c r="I118" s="11" t="n"/>
+      <c r="J118" s="11" t="n"/>
+      <c r="K118" s="11" t="n"/>
+      <c r="L118" s="11" t="n"/>
+      <c r="M118" s="11" t="n"/>
+      <c r="N118" s="11" t="n"/>
+      <c r="O118" s="12" t="n">
+        <v>2856.26</v>
+      </c>
+      <c r="P118" s="12" t="n">
         <v>2090</v>
       </c>
-      <c r="Q118" s="12" t="inlineStr">
+      <c r="Q118" s="11" t="inlineStr">
         <is>
           <t>Advanced's invoice pricing, order 4647520</t>
         </is>
       </c>
-      <c r="R118" s="12" t="n">
+      <c r="R118" s="11" t="n">
         <v>117.5</v>
       </c>
-      <c r="S118" s="12" t="n">
+      <c r="S118" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="T118" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" s="12" t="n">
+      <c r="T118" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="V118" s="12" t="inlineStr">
+      <c r="V118" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -9905,10 +9874,10 @@
       <c r="L119" s="2" t="n"/>
       <c r="M119" s="2" t="n"/>
       <c r="N119" s="2" t="n"/>
-      <c r="O119" s="7" t="n">
+      <c r="O119" s="6" t="n">
         <v>2464.51</v>
       </c>
-      <c r="P119" s="7" t="n">
+      <c r="P119" s="6" t="n">
         <v>1675</v>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -9967,10 +9936,10 @@
       <c r="L120" s="2" t="n"/>
       <c r="M120" s="2" t="n"/>
       <c r="N120" s="2" t="n"/>
-      <c r="O120" s="7" t="n">
+      <c r="O120" s="6" t="n">
         <v>6513.96</v>
       </c>
-      <c r="P120" s="7" t="n">
+      <c r="P120" s="6" t="n">
         <v>4458.5</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -10025,10 +9994,10 @@
       <c r="L121" s="2" t="n"/>
       <c r="M121" s="2" t="n"/>
       <c r="N121" s="2" t="n"/>
-      <c r="O121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" s="7" t="n">
+      <c r="O121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="6" t="n">
         <v>100</v>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -10085,10 +10054,10 @@
       <c r="L122" s="2" t="n"/>
       <c r="M122" s="2" t="n"/>
       <c r="N122" s="2" t="n"/>
-      <c r="O122" s="7" t="n">
+      <c r="O122" s="6" t="n">
         <v>40.4</v>
       </c>
-      <c r="P122" s="7" t="n">
+      <c r="P122" s="6" t="n">
         <v>25</v>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -10145,10 +10114,10 @@
       <c r="L123" s="2" t="n"/>
       <c r="M123" s="2" t="n"/>
       <c r="N123" s="2" t="n"/>
-      <c r="O123" s="7" t="n">
+      <c r="O123" s="6" t="n">
         <v>2100.89</v>
       </c>
-      <c r="P123" s="7" t="n">
+      <c r="P123" s="6" t="n">
         <v>1450</v>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -10207,10 +10176,10 @@
       <c r="L124" s="2" t="n"/>
       <c r="M124" s="2" t="n"/>
       <c r="N124" s="2" t="n"/>
-      <c r="O124" s="7" t="n">
+      <c r="O124" s="6" t="n">
         <v>2883.67</v>
       </c>
-      <c r="P124" s="7" t="n">
+      <c r="P124" s="6" t="n">
         <v>1515</v>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -10261,10 +10230,10 @@
       <c r="L125" s="2" t="n"/>
       <c r="M125" s="2" t="n"/>
       <c r="N125" s="2" t="n"/>
-      <c r="O125" s="7" t="n">
+      <c r="O125" s="6" t="n">
         <v>525.22</v>
       </c>
-      <c r="P125" s="7" t="n">
+      <c r="P125" s="6" t="n">
         <v>325</v>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -10283,58 +10252,58 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="12" t="inlineStr">
+      <c r="A126" s="11" t="inlineStr">
         <is>
           <t>36625</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="C126" s="12" t="inlineStr">
+      <c r="C126" s="11" t="inlineStr">
         <is>
           <t>Event Week</t>
         </is>
       </c>
-      <c r="D126" s="12" t="inlineStr">
+      <c r="D126" s="11" t="inlineStr">
         <is>
           <t>Gate 1 - S23 Compound</t>
         </is>
       </c>
-      <c r="E126" s="12" t="n">
+      <c r="E126" s="11" t="n">
         <v>285</v>
       </c>
-      <c r="F126" s="12" t="n">
+      <c r="F126" s="11" t="n">
         <v>285</v>
       </c>
-      <c r="G126" s="12" t="n"/>
-      <c r="H126" s="12" t="n"/>
-      <c r="I126" s="12" t="n"/>
-      <c r="J126" s="12" t="n"/>
-      <c r="K126" s="12" t="n"/>
-      <c r="L126" s="12" t="n"/>
-      <c r="M126" s="12" t="n"/>
-      <c r="N126" s="12" t="n"/>
-      <c r="O126" s="13" t="n">
-        <v>11881.85</v>
-      </c>
-      <c r="P126" s="13" t="n">
-        <v>9804</v>
-      </c>
-      <c r="Q126" s="12" t="inlineStr">
+      <c r="G126" s="11" t="n"/>
+      <c r="H126" s="11" t="n"/>
+      <c r="I126" s="11" t="n"/>
+      <c r="J126" s="11" t="n"/>
+      <c r="K126" s="11" t="n"/>
+      <c r="L126" s="11" t="n"/>
+      <c r="M126" s="11" t="n"/>
+      <c r="N126" s="11" t="n"/>
+      <c r="O126" s="12" t="n">
+        <v>7276.05</v>
+      </c>
+      <c r="P126" s="12" t="n">
+        <v>6954</v>
+      </c>
+      <c r="Q126" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R126" s="12" t="n"/>
-      <c r="S126" s="12" t="n"/>
-      <c r="T126" s="12" t="n"/>
-      <c r="U126" s="12" t="n">
+      <c r="R126" s="11" t="n"/>
+      <c r="S126" s="11" t="n"/>
+      <c r="T126" s="11" t="n"/>
+      <c r="U126" s="11" t="n">
         <v>285</v>
       </c>
-      <c r="V126" s="12" t="inlineStr">
+      <c r="V126" s="11" t="inlineStr">
         <is>
           <t>event week: not billed yet</t>
         </is>
@@ -10373,10 +10342,10 @@
       <c r="L127" s="2" t="n"/>
       <c r="M127" s="2" t="n"/>
       <c r="N127" s="2" t="n"/>
-      <c r="O127" s="7" t="n">
+      <c r="O127" s="6" t="n">
         <v>7959.14</v>
       </c>
-      <c r="P127" s="7" t="n">
+      <c r="P127" s="6" t="n">
         <v>4925</v>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -10429,10 +10398,10 @@
       <c r="L128" s="2" t="n"/>
       <c r="M128" s="2" t="n"/>
       <c r="N128" s="2" t="n"/>
-      <c r="O128" s="7" t="n">
+      <c r="O128" s="6" t="n">
         <v>1036.85</v>
       </c>
-      <c r="P128" s="7" t="n">
+      <c r="P128" s="6" t="n">
         <v>715.5</v>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -10451,118 +10420,118 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="12" t="inlineStr">
+      <c r="A129" s="11" t="inlineStr">
         <is>
           <t>36628</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B129" s="11" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C129" s="12" t="inlineStr">
+      <c r="C129" s="11" t="inlineStr">
         <is>
           <t>Event Week</t>
         </is>
       </c>
-      <c r="D129" s="12" t="inlineStr">
+      <c r="D129" s="11" t="inlineStr">
         <is>
           <t>PB03 - footings</t>
         </is>
       </c>
-      <c r="E129" s="12" t="n">
+      <c r="E129" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="F129" s="12" t="n">
+      <c r="F129" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G129" s="12" t="n"/>
-      <c r="H129" s="12" t="n"/>
-      <c r="I129" s="12" t="n"/>
-      <c r="J129" s="12" t="n"/>
-      <c r="K129" s="12" t="n"/>
-      <c r="L129" s="12" t="n"/>
-      <c r="M129" s="12" t="n"/>
-      <c r="N129" s="12" t="n"/>
-      <c r="O129" s="13" t="n">
-        <v>1042.27</v>
-      </c>
-      <c r="P129" s="13" t="n">
-        <v>860</v>
-      </c>
-      <c r="Q129" s="12" t="inlineStr">
+      <c r="G129" s="11" t="n"/>
+      <c r="H129" s="11" t="n"/>
+      <c r="I129" s="11" t="n"/>
+      <c r="J129" s="11" t="n"/>
+      <c r="K129" s="11" t="n"/>
+      <c r="L129" s="11" t="n"/>
+      <c r="M129" s="11" t="n"/>
+      <c r="N129" s="11" t="n"/>
+      <c r="O129" s="12" t="n">
+        <v>638.25</v>
+      </c>
+      <c r="P129" s="12" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q129" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R129" s="12" t="n"/>
-      <c r="S129" s="12" t="n"/>
-      <c r="T129" s="12" t="n"/>
-      <c r="U129" s="12" t="n">
+      <c r="R129" s="11" t="n"/>
+      <c r="S129" s="11" t="n"/>
+      <c r="T129" s="11" t="n"/>
+      <c r="U129" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="V129" s="12" t="inlineStr">
+      <c r="V129" s="11" t="inlineStr">
         <is>
           <t>event week: not billed yet</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="12" t="inlineStr">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t>36629</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
+      <c r="B130" s="11" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C130" s="12" t="inlineStr">
+      <c r="C130" s="11" t="inlineStr">
         <is>
           <t>Event Week</t>
         </is>
       </c>
-      <c r="D130" s="12" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>PB03 - Gate 1 - Helen Park</t>
         </is>
       </c>
-      <c r="E130" s="12" t="n"/>
-      <c r="F130" s="12" t="n">
+      <c r="E130" s="11" t="n"/>
+      <c r="F130" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="G130" s="12" t="n">
+      <c r="G130" s="11" t="n">
         <v>182.5</v>
       </c>
-      <c r="H130" s="12" t="n">
+      <c r="H130" s="11" t="n">
         <v>237.5</v>
       </c>
-      <c r="I130" s="12" t="n"/>
-      <c r="J130" s="12" t="n"/>
-      <c r="K130" s="12" t="n"/>
-      <c r="L130" s="12" t="n"/>
-      <c r="M130" s="12" t="n"/>
-      <c r="N130" s="12" t="n"/>
-      <c r="O130" s="13" t="n">
-        <v>6213.13</v>
-      </c>
-      <c r="P130" s="13" t="n">
-        <v>4220</v>
-      </c>
-      <c r="Q130" s="12" t="inlineStr">
+      <c r="I130" s="11" t="n"/>
+      <c r="J130" s="11" t="n"/>
+      <c r="K130" s="11" t="n"/>
+      <c r="L130" s="11" t="n"/>
+      <c r="M130" s="11" t="n"/>
+      <c r="N130" s="11" t="n"/>
+      <c r="O130" s="12" t="n">
+        <v>4920.27</v>
+      </c>
+      <c r="P130" s="12" t="n">
+        <v>3420</v>
+      </c>
+      <c r="Q130" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R130" s="12" t="n"/>
-      <c r="S130" s="12" t="n"/>
-      <c r="T130" s="12" t="n"/>
-      <c r="U130" s="12" t="n">
+      <c r="R130" s="11" t="n"/>
+      <c r="S130" s="11" t="n"/>
+      <c r="T130" s="11" t="n"/>
+      <c r="U130" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="V130" s="12" t="inlineStr">
+      <c r="V130" s="11" t="inlineStr">
         <is>
           <t>event week: not billed yet</t>
         </is>
@@ -10601,10 +10570,10 @@
       <c r="L131" s="2" t="n"/>
       <c r="M131" s="2" t="n"/>
       <c r="N131" s="2" t="n"/>
-      <c r="O131" s="7" t="n">
+      <c r="O131" s="6" t="n">
         <v>484.82</v>
       </c>
-      <c r="P131" s="7" t="n">
+      <c r="P131" s="6" t="n">
         <v>300</v>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -10623,58 +10592,58 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="12" t="inlineStr">
+      <c r="A132" s="11" t="inlineStr">
         <is>
           <t>36631</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C132" s="12" t="inlineStr">
+      <c r="C132" s="11" t="inlineStr">
         <is>
           <t>Event Week</t>
         </is>
       </c>
-      <c r="D132" s="12" t="inlineStr">
+      <c r="D132" s="11" t="inlineStr">
         <is>
           <t>Podium</t>
         </is>
       </c>
-      <c r="E132" s="12" t="n">
+      <c r="E132" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F132" s="12" t="n">
+      <c r="F132" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G132" s="12" t="n"/>
-      <c r="H132" s="12" t="n"/>
-      <c r="I132" s="12" t="n"/>
-      <c r="J132" s="12" t="n"/>
-      <c r="K132" s="12" t="n"/>
-      <c r="L132" s="12" t="n"/>
-      <c r="M132" s="12" t="n"/>
-      <c r="N132" s="12" t="n"/>
-      <c r="O132" s="13" t="n">
-        <v>208.45</v>
-      </c>
-      <c r="P132" s="13" t="n">
-        <v>172</v>
-      </c>
-      <c r="Q132" s="12" t="inlineStr">
+      <c r="G132" s="11" t="n"/>
+      <c r="H132" s="11" t="n"/>
+      <c r="I132" s="11" t="n"/>
+      <c r="J132" s="11" t="n"/>
+      <c r="K132" s="11" t="n"/>
+      <c r="L132" s="11" t="n"/>
+      <c r="M132" s="11" t="n"/>
+      <c r="N132" s="11" t="n"/>
+      <c r="O132" s="12" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="P132" s="12" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q132" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R132" s="12" t="n"/>
-      <c r="S132" s="12" t="n"/>
-      <c r="T132" s="12" t="n"/>
-      <c r="U132" s="12" t="n">
+      <c r="R132" s="11" t="n"/>
+      <c r="S132" s="11" t="n"/>
+      <c r="T132" s="11" t="n"/>
+      <c r="U132" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="V132" s="12" t="inlineStr">
+      <c r="V132" s="11" t="inlineStr">
         <is>
           <t>event week: not billed yet</t>
         </is>
@@ -10711,10 +10680,10 @@
       <c r="L133" s="2" t="n"/>
       <c r="M133" s="2" t="n"/>
       <c r="N133" s="2" t="n"/>
-      <c r="O133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" s="7" t="n">
+      <c r="O133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -10765,10 +10734,10 @@
       <c r="L134" s="2" t="n"/>
       <c r="M134" s="2" t="n"/>
       <c r="N134" s="2" t="n"/>
-      <c r="O134" s="7" t="n">
+      <c r="O134" s="6" t="n">
         <v>282.81</v>
       </c>
-      <c r="P134" s="7" t="n">
+      <c r="P134" s="6" t="n">
         <v>175</v>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -10819,10 +10788,10 @@
       <c r="L135" s="2" t="n"/>
       <c r="M135" s="2" t="n"/>
       <c r="N135" s="2" t="n"/>
-      <c r="O135" s="7" t="n">
+      <c r="O135" s="6" t="n">
         <v>163.5</v>
       </c>
-      <c r="P135" s="7" t="n">
+      <c r="P135" s="6" t="n">
         <v>67.5</v>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -10875,10 +10844,10 @@
       <c r="L136" s="2" t="n"/>
       <c r="M136" s="2" t="n"/>
       <c r="N136" s="2" t="n"/>
-      <c r="O136" s="7" t="n">
+      <c r="O136" s="6" t="n">
         <v>619.42</v>
       </c>
-      <c r="P136" s="7" t="n">
+      <c r="P136" s="6" t="n">
         <v>391.5</v>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -10929,10 +10898,10 @@
       <c r="L137" s="2" t="n"/>
       <c r="M137" s="2" t="n"/>
       <c r="N137" s="2" t="n"/>
-      <c r="O137" s="7" t="n">
+      <c r="O137" s="6" t="n">
         <v>2681.4</v>
       </c>
-      <c r="P137" s="7" t="n">
+      <c r="P137" s="6" t="n">
         <v>1107</v>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -10983,10 +10952,10 @@
       <c r="L138" s="2" t="n"/>
       <c r="M138" s="2" t="n"/>
       <c r="N138" s="2" t="n"/>
-      <c r="O138" s="7" t="n">
+      <c r="O138" s="6" t="n">
         <v>187.75</v>
       </c>
-      <c r="P138" s="7" t="n">
+      <c r="P138" s="6" t="n">
         <v>135</v>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -11037,10 +11006,10 @@
       <c r="L139" s="2" t="n"/>
       <c r="M139" s="2" t="n"/>
       <c r="N139" s="2" t="n"/>
-      <c r="O139" s="7" t="n">
+      <c r="O139" s="6" t="n">
         <v>849.3</v>
       </c>
-      <c r="P139" s="7" t="n">
+      <c r="P139" s="6" t="n">
         <v>475.2</v>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -11059,58 +11028,58 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="12" t="inlineStr">
+      <c r="A140" s="11" t="inlineStr">
         <is>
           <t>36639</t>
         </is>
       </c>
-      <c r="B140" s="12" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C140" s="12" t="inlineStr">
+      <c r="C140" s="11" t="inlineStr">
         <is>
           <t>Event Week</t>
         </is>
       </c>
-      <c r="D140" s="12" t="inlineStr">
+      <c r="D140" s="11" t="inlineStr">
         <is>
           <t>McIntosh Island storage</t>
         </is>
       </c>
-      <c r="E140" s="12" t="n">
+      <c r="E140" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="F140" s="12" t="n">
+      <c r="F140" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="G140" s="12" t="n"/>
-      <c r="H140" s="12" t="n"/>
-      <c r="I140" s="12" t="n"/>
-      <c r="J140" s="12" t="n"/>
-      <c r="K140" s="12" t="n"/>
-      <c r="L140" s="12" t="n"/>
-      <c r="M140" s="12" t="n"/>
-      <c r="N140" s="12" t="n"/>
-      <c r="O140" s="13" t="n">
-        <v>625.36</v>
-      </c>
-      <c r="P140" s="13" t="n">
-        <v>516</v>
-      </c>
-      <c r="Q140" s="12" t="inlineStr">
+      <c r="G140" s="11" t="n"/>
+      <c r="H140" s="11" t="n"/>
+      <c r="I140" s="11" t="n"/>
+      <c r="J140" s="11" t="n"/>
+      <c r="K140" s="11" t="n"/>
+      <c r="L140" s="11" t="n"/>
+      <c r="M140" s="11" t="n"/>
+      <c r="N140" s="11" t="n"/>
+      <c r="O140" s="12" t="n">
+        <v>382.95</v>
+      </c>
+      <c r="P140" s="12" t="n">
+        <v>366</v>
+      </c>
+      <c r="Q140" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R140" s="12" t="n"/>
-      <c r="S140" s="12" t="n"/>
-      <c r="T140" s="12" t="n"/>
-      <c r="U140" s="12" t="n">
+      <c r="R140" s="11" t="n"/>
+      <c r="S140" s="11" t="n"/>
+      <c r="T140" s="11" t="n"/>
+      <c r="U140" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="V140" s="12" t="inlineStr">
+      <c r="V140" s="11" t="inlineStr">
         <is>
           <t>event week: not billed yet</t>
         </is>
@@ -11149,10 +11118,10 @@
       <c r="L141" s="2" t="n"/>
       <c r="M141" s="2" t="n"/>
       <c r="N141" s="2" t="n"/>
-      <c r="O141" s="7" t="n">
+      <c r="O141" s="6" t="n">
         <v>767.63</v>
       </c>
-      <c r="P141" s="7" t="n">
+      <c r="P141" s="6" t="n">
         <v>475</v>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -11171,118 +11140,118 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="12" t="inlineStr">
+      <c r="A142" s="11" t="inlineStr">
         <is>
           <t>36642</t>
         </is>
       </c>
-      <c r="B142" s="12" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C142" s="12" t="inlineStr">
+      <c r="C142" s="11" t="inlineStr">
         <is>
           <t>Event Week</t>
         </is>
       </c>
-      <c r="D142" s="12" t="inlineStr">
+      <c r="D142" s="11" t="inlineStr">
         <is>
           <t>Gate 6</t>
         </is>
       </c>
-      <c r="E142" s="12" t="n">
+      <c r="E142" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="F142" s="12" t="n">
+      <c r="F142" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="G142" s="12" t="n"/>
-      <c r="H142" s="12" t="n"/>
-      <c r="I142" s="12" t="n"/>
-      <c r="J142" s="12" t="n"/>
-      <c r="K142" s="12" t="n"/>
-      <c r="L142" s="12" t="n"/>
-      <c r="M142" s="12" t="n"/>
-      <c r="N142" s="12" t="n"/>
-      <c r="O142" s="13" t="n">
-        <v>312.69</v>
-      </c>
-      <c r="P142" s="13" t="n">
-        <v>258</v>
-      </c>
-      <c r="Q142" s="12" t="inlineStr">
+      <c r="G142" s="11" t="n"/>
+      <c r="H142" s="11" t="n"/>
+      <c r="I142" s="11" t="n"/>
+      <c r="J142" s="11" t="n"/>
+      <c r="K142" s="11" t="n"/>
+      <c r="L142" s="11" t="n"/>
+      <c r="M142" s="11" t="n"/>
+      <c r="N142" s="11" t="n"/>
+      <c r="O142" s="12" t="n">
+        <v>191.48</v>
+      </c>
+      <c r="P142" s="12" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q142" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R142" s="12" t="n"/>
-      <c r="S142" s="12" t="n"/>
-      <c r="T142" s="12" t="n"/>
-      <c r="U142" s="12" t="n">
+      <c r="R142" s="11" t="n"/>
+      <c r="S142" s="11" t="n"/>
+      <c r="T142" s="11" t="n"/>
+      <c r="U142" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="V142" s="12" t="inlineStr">
+      <c r="V142" s="11" t="inlineStr">
         <is>
           <t>event week: not billed yet</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="12" t="inlineStr">
+      <c r="A143" s="11" t="inlineStr">
         <is>
           <t>36643</t>
         </is>
       </c>
-      <c r="B143" s="12" t="inlineStr">
+      <c r="B143" s="11" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C143" s="12" t="inlineStr">
+      <c r="C143" s="11" t="inlineStr">
         <is>
           <t>Event Week</t>
         </is>
       </c>
-      <c r="D143" s="12" t="inlineStr">
+      <c r="D143" s="11" t="inlineStr">
         <is>
           <t>Club 500</t>
         </is>
       </c>
-      <c r="E143" s="12" t="n">
+      <c r="E143" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="F143" s="12" t="n">
+      <c r="F143" s="11" t="n">
         <v>47.5</v>
       </c>
-      <c r="G143" s="12" t="n"/>
-      <c r="H143" s="12" t="n">
+      <c r="G143" s="11" t="n"/>
+      <c r="H143" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="I143" s="12" t="n"/>
-      <c r="J143" s="12" t="n"/>
-      <c r="K143" s="12" t="n"/>
-      <c r="L143" s="12" t="n"/>
-      <c r="M143" s="12" t="n"/>
-      <c r="N143" s="12" t="n"/>
-      <c r="O143" s="13" t="n">
-        <v>1888.1</v>
-      </c>
-      <c r="P143" s="13" t="n">
-        <v>1592</v>
-      </c>
-      <c r="Q143" s="12" t="inlineStr">
+      <c r="I143" s="11" t="n"/>
+      <c r="J143" s="11" t="n"/>
+      <c r="K143" s="11" t="n"/>
+      <c r="L143" s="11" t="n"/>
+      <c r="M143" s="11" t="n"/>
+      <c r="N143" s="11" t="n"/>
+      <c r="O143" s="12" t="n">
+        <v>1120.47</v>
+      </c>
+      <c r="P143" s="12" t="n">
+        <v>1117</v>
+      </c>
+      <c r="Q143" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R143" s="12" t="n"/>
-      <c r="S143" s="12" t="n"/>
-      <c r="T143" s="12" t="n"/>
-      <c r="U143" s="12" t="n">
+      <c r="R143" s="11" t="n"/>
+      <c r="S143" s="11" t="n"/>
+      <c r="T143" s="11" t="n"/>
+      <c r="U143" s="11" t="n">
         <v>47.5</v>
       </c>
-      <c r="V143" s="12" t="inlineStr">
+      <c r="V143" s="11" t="inlineStr">
         <is>
           <t>event week: not billed yet</t>
         </is>
@@ -11319,10 +11288,10 @@
       <c r="L144" s="2" t="n"/>
       <c r="M144" s="2" t="n"/>
       <c r="N144" s="2" t="n"/>
-      <c r="O144" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" s="7" t="n">
+      <c r="O144" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -11373,10 +11342,10 @@
       <c r="L145" s="2" t="n"/>
       <c r="M145" s="2" t="n"/>
       <c r="N145" s="2" t="n"/>
-      <c r="O145" s="7" t="n">
+      <c r="O145" s="6" t="n">
         <v>163.5</v>
       </c>
-      <c r="P145" s="7" t="n">
+      <c r="P145" s="6" t="n">
         <v>67.5</v>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -11427,10 +11396,10 @@
       <c r="L146" s="2" t="n"/>
       <c r="M146" s="2" t="n"/>
       <c r="N146" s="2" t="n"/>
-      <c r="O146" s="7" t="n">
+      <c r="O146" s="6" t="n">
         <v>242.41</v>
       </c>
-      <c r="P146" s="7" t="n">
+      <c r="P146" s="6" t="n">
         <v>150</v>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -11481,10 +11450,10 @@
       <c r="L147" s="2" t="n"/>
       <c r="M147" s="2" t="n"/>
       <c r="N147" s="2" t="n"/>
-      <c r="O147" s="7" t="n">
+      <c r="O147" s="6" t="n">
         <v>356.73</v>
       </c>
-      <c r="P147" s="7" t="n">
+      <c r="P147" s="6" t="n">
         <v>256.5</v>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -11535,10 +11504,10 @@
       <c r="L148" s="2" t="n"/>
       <c r="M148" s="2" t="n"/>
       <c r="N148" s="2" t="n"/>
-      <c r="O148" s="7" t="n">
+      <c r="O148" s="6" t="n">
         <v>161.61</v>
       </c>
-      <c r="P148" s="7" t="n">
+      <c r="P148" s="6" t="n">
         <v>100</v>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -11589,10 +11558,10 @@
       <c r="L149" s="2" t="n"/>
       <c r="M149" s="2" t="n"/>
       <c r="N149" s="2" t="n"/>
-      <c r="O149" s="7" t="n">
+      <c r="O149" s="6" t="n">
         <v>1131.25</v>
       </c>
-      <c r="P149" s="7" t="n">
+      <c r="P149" s="6" t="n">
         <v>700</v>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -11643,10 +11612,10 @@
       <c r="L150" s="2" t="n"/>
       <c r="M150" s="2" t="n"/>
       <c r="N150" s="2" t="n"/>
-      <c r="O150" s="7" t="n">
+      <c r="O150" s="6" t="n">
         <v>606.03</v>
       </c>
-      <c r="P150" s="7" t="n">
+      <c r="P150" s="6" t="n">
         <v>375</v>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -11665,58 +11634,58 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="12" t="inlineStr">
+      <c r="A151" s="11" t="inlineStr">
         <is>
           <t>36649</t>
         </is>
       </c>
-      <c r="B151" s="12" t="inlineStr">
+      <c r="B151" s="11" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C151" s="12" t="inlineStr">
+      <c r="C151" s="11" t="inlineStr">
         <is>
           <t>Event Week</t>
         </is>
       </c>
-      <c r="D151" s="12" t="inlineStr">
+      <c r="D151" s="11" t="inlineStr">
         <is>
           <t>Gate 10</t>
         </is>
       </c>
-      <c r="E151" s="12" t="n">
+      <c r="E151" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="F151" s="12" t="n">
+      <c r="F151" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="G151" s="12" t="n"/>
-      <c r="H151" s="12" t="n"/>
-      <c r="I151" s="12" t="n"/>
-      <c r="J151" s="12" t="n"/>
-      <c r="K151" s="12" t="n"/>
-      <c r="L151" s="12" t="n"/>
-      <c r="M151" s="12" t="n"/>
-      <c r="N151" s="12" t="n"/>
-      <c r="O151" s="13" t="n">
-        <v>1667.63</v>
-      </c>
-      <c r="P151" s="13" t="n">
-        <v>1376</v>
-      </c>
-      <c r="Q151" s="12" t="inlineStr">
+      <c r="G151" s="11" t="n"/>
+      <c r="H151" s="11" t="n"/>
+      <c r="I151" s="11" t="n"/>
+      <c r="J151" s="11" t="n"/>
+      <c r="K151" s="11" t="n"/>
+      <c r="L151" s="11" t="n"/>
+      <c r="M151" s="11" t="n"/>
+      <c r="N151" s="11" t="n"/>
+      <c r="O151" s="12" t="n">
+        <v>1021.2</v>
+      </c>
+      <c r="P151" s="12" t="n">
+        <v>976</v>
+      </c>
+      <c r="Q151" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R151" s="12" t="n"/>
-      <c r="S151" s="12" t="n"/>
-      <c r="T151" s="12" t="n"/>
-      <c r="U151" s="12" t="n">
+      <c r="R151" s="11" t="n"/>
+      <c r="S151" s="11" t="n"/>
+      <c r="T151" s="11" t="n"/>
+      <c r="U151" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="V151" s="12" t="inlineStr">
+      <c r="V151" s="11" t="inlineStr">
         <is>
           <t>event week: not billed yet</t>
         </is>
@@ -11755,10 +11724,10 @@
       <c r="L152" s="2" t="n"/>
       <c r="M152" s="2" t="n"/>
       <c r="N152" s="2" t="n"/>
-      <c r="O152" s="7" t="n">
+      <c r="O152" s="6" t="n">
         <v>80.8</v>
       </c>
-      <c r="P152" s="7" t="n">
+      <c r="P152" s="6" t="n">
         <v>50</v>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -11811,10 +11780,10 @@
       <c r="L153" s="2" t="n"/>
       <c r="M153" s="2" t="n"/>
       <c r="N153" s="2" t="n"/>
-      <c r="O153" s="7" t="n">
+      <c r="O153" s="6" t="n">
         <v>4749.35</v>
       </c>
-      <c r="P153" s="7" t="n">
+      <c r="P153" s="6" t="n">
         <v>3176</v>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -11865,10 +11834,10 @@
       <c r="L154" s="2" t="n"/>
       <c r="M154" s="2" t="n"/>
       <c r="N154" s="2" t="n"/>
-      <c r="O154" s="7" t="n">
+      <c r="O154" s="6" t="n">
         <v>323.21</v>
       </c>
-      <c r="P154" s="7" t="n">
+      <c r="P154" s="6" t="n">
         <v>200</v>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -11919,10 +11888,10 @@
       <c r="L155" s="2" t="n"/>
       <c r="M155" s="2" t="n"/>
       <c r="N155" s="2" t="n"/>
-      <c r="O155" s="7" t="n">
+      <c r="O155" s="6" t="n">
         <v>282.81</v>
       </c>
-      <c r="P155" s="7" t="n">
+      <c r="P155" s="6" t="n">
         <v>175</v>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -11973,10 +11942,10 @@
       <c r="L156" s="2" t="n"/>
       <c r="M156" s="2" t="n"/>
       <c r="N156" s="2" t="n"/>
-      <c r="O156" s="7" t="n">
+      <c r="O156" s="6" t="n">
         <v>606.03</v>
       </c>
-      <c r="P156" s="7" t="n">
+      <c r="P156" s="6" t="n">
         <v>375</v>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -12029,10 +11998,10 @@
       <c r="L157" s="2" t="n"/>
       <c r="M157" s="2" t="n"/>
       <c r="N157" s="2" t="n"/>
-      <c r="O157" s="7" t="n">
+      <c r="O157" s="6" t="n">
         <v>903.5700000000001</v>
       </c>
-      <c r="P157" s="7" t="n">
+      <c r="P157" s="6" t="n">
         <v>593</v>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -12083,10 +12052,10 @@
       <c r="L158" s="2" t="n"/>
       <c r="M158" s="2" t="n"/>
       <c r="N158" s="2" t="n"/>
-      <c r="O158" s="7" t="n">
+      <c r="O158" s="6" t="n">
         <v>484.82</v>
       </c>
-      <c r="P158" s="7" t="n">
+      <c r="P158" s="6" t="n">
         <v>300</v>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -12105,58 +12074,58 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="12" t="inlineStr">
+      <c r="A159" s="11" t="inlineStr">
         <is>
           <t>36759</t>
         </is>
       </c>
-      <c r="B159" s="12" t="inlineStr">
+      <c r="B159" s="11" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C159" s="12" t="inlineStr">
+      <c r="C159" s="11" t="inlineStr">
         <is>
           <t>Event Week</t>
         </is>
       </c>
-      <c r="D159" s="12" t="inlineStr">
+      <c r="D159" s="11" t="inlineStr">
         <is>
           <t>Rhapsody Sales Office - walk through</t>
         </is>
       </c>
-      <c r="E159" s="12" t="n">
+      <c r="E159" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="F159" s="12" t="n">
+      <c r="F159" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="G159" s="12" t="n"/>
-      <c r="H159" s="12" t="n"/>
-      <c r="I159" s="12" t="n"/>
-      <c r="J159" s="12" t="n"/>
-      <c r="K159" s="12" t="n"/>
-      <c r="L159" s="12" t="n"/>
-      <c r="M159" s="12" t="n"/>
-      <c r="N159" s="12" t="n"/>
-      <c r="O159" s="13" t="n">
-        <v>3022.58</v>
-      </c>
-      <c r="P159" s="13" t="n">
-        <v>2494</v>
-      </c>
-      <c r="Q159" s="12" t="inlineStr">
+      <c r="G159" s="11" t="n"/>
+      <c r="H159" s="11" t="n"/>
+      <c r="I159" s="11" t="n"/>
+      <c r="J159" s="11" t="n"/>
+      <c r="K159" s="11" t="n"/>
+      <c r="L159" s="11" t="n"/>
+      <c r="M159" s="11" t="n"/>
+      <c r="N159" s="11" t="n"/>
+      <c r="O159" s="12" t="n">
+        <v>1850.93</v>
+      </c>
+      <c r="P159" s="12" t="n">
+        <v>1769</v>
+      </c>
+      <c r="Q159" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R159" s="12" t="n"/>
-      <c r="S159" s="12" t="n"/>
-      <c r="T159" s="12" t="n"/>
-      <c r="U159" s="12" t="n">
+      <c r="R159" s="11" t="n"/>
+      <c r="S159" s="11" t="n"/>
+      <c r="T159" s="11" t="n"/>
+      <c r="U159" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="V159" s="12" t="inlineStr">
+      <c r="V159" s="11" t="inlineStr">
         <is>
           <t>event week: not billed yet</t>
         </is>
@@ -12195,10 +12164,10 @@
       <c r="L160" s="2" t="n"/>
       <c r="M160" s="2" t="n"/>
       <c r="N160" s="2" t="n"/>
-      <c r="O160" s="7" t="n">
+      <c r="O160" s="6" t="n">
         <v>130.8</v>
       </c>
-      <c r="P160" s="7" t="n">
+      <c r="P160" s="6" t="n">
         <v>54</v>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -12217,58 +12186,58 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="12" t="inlineStr">
+      <c r="A161" s="11" t="inlineStr">
         <is>
           <t>36761</t>
         </is>
       </c>
-      <c r="B161" s="12" t="inlineStr">
+      <c r="B161" s="11" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C161" s="12" t="inlineStr">
+      <c r="C161" s="11" t="inlineStr">
         <is>
           <t>Event Week</t>
         </is>
       </c>
-      <c r="D161" s="12" t="inlineStr">
+      <c r="D161" s="11" t="inlineStr">
         <is>
           <t>Rubbish Compactor (Cleanaway)</t>
         </is>
       </c>
-      <c r="E161" s="12" t="n">
+      <c r="E161" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="F161" s="12" t="n">
+      <c r="F161" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="G161" s="12" t="n"/>
-      <c r="H161" s="12" t="n"/>
-      <c r="I161" s="12" t="n"/>
-      <c r="J161" s="12" t="n"/>
-      <c r="K161" s="12" t="n"/>
-      <c r="L161" s="12" t="n"/>
-      <c r="M161" s="12" t="n"/>
-      <c r="N161" s="12" t="n"/>
-      <c r="O161" s="13" t="n">
-        <v>1395.35</v>
-      </c>
-      <c r="P161" s="13" t="n">
-        <v>1143</v>
-      </c>
-      <c r="Q161" s="12" t="inlineStr">
+      <c r="G161" s="11" t="n"/>
+      <c r="H161" s="11" t="n"/>
+      <c r="I161" s="11" t="n"/>
+      <c r="J161" s="11" t="n"/>
+      <c r="K161" s="11" t="n"/>
+      <c r="L161" s="11" t="n"/>
+      <c r="M161" s="11" t="n"/>
+      <c r="N161" s="11" t="n"/>
+      <c r="O161" s="12" t="n">
+        <v>870.13</v>
+      </c>
+      <c r="P161" s="12" t="n">
+        <v>818</v>
+      </c>
+      <c r="Q161" s="11" t="inlineStr">
         <is>
           <t>Advanced's rate sheet</t>
         </is>
       </c>
-      <c r="R161" s="12" t="n"/>
-      <c r="S161" s="12" t="n"/>
-      <c r="T161" s="12" t="n"/>
-      <c r="U161" s="12" t="n">
+      <c r="R161" s="11" t="n"/>
+      <c r="S161" s="11" t="n"/>
+      <c r="T161" s="11" t="n"/>
+      <c r="U161" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="V161" s="12" t="inlineStr">
+      <c r="V161" s="11" t="inlineStr">
         <is>
           <t>event week: not billed yet</t>
         </is>
@@ -12307,10 +12276,10 @@
       <c r="L162" s="2" t="n"/>
       <c r="M162" s="2" t="n"/>
       <c r="N162" s="2" t="n"/>
-      <c r="O162" s="7" t="n">
+      <c r="O162" s="6" t="n">
         <v>323.21</v>
       </c>
-      <c r="P162" s="7" t="n">
+      <c r="P162" s="6" t="n">
         <v>200</v>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -12359,10 +12328,10 @@
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n"/>
       <c r="N163" s="2" t="n"/>
-      <c r="O163" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" s="7" t="n">
+      <c r="O163" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -12413,10 +12382,10 @@
       <c r="L164" s="2" t="n"/>
       <c r="M164" s="2" t="n"/>
       <c r="N164" s="2" t="n"/>
-      <c r="O164" s="7" t="n">
+      <c r="O164" s="6" t="n">
         <v>112.65</v>
       </c>
-      <c r="P164" s="7" t="n">
+      <c r="P164" s="6" t="n">
         <v>81</v>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -12467,10 +12436,10 @@
       <c r="L165" s="2" t="n"/>
       <c r="M165" s="2" t="n"/>
       <c r="N165" s="2" t="n"/>
-      <c r="O165" s="7" t="n">
+      <c r="O165" s="6" t="n">
         <v>80.8</v>
       </c>
-      <c r="P165" s="7" t="n">
+      <c r="P165" s="6" t="n">
         <v>50</v>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -12521,10 +12490,10 @@
       <c r="L166" s="2" t="n"/>
       <c r="M166" s="2" t="n"/>
       <c r="N166" s="2" t="n"/>
-      <c r="O166" s="7" t="n">
+      <c r="O166" s="6" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="P166" s="7" t="n">
+      <c r="P166" s="6" t="n">
         <v>54</v>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -12575,10 +12544,10 @@
       <c r="L167" s="2" t="n"/>
       <c r="M167" s="2" t="n"/>
       <c r="N167" s="2" t="n"/>
-      <c r="O167" s="7" t="n">
+      <c r="O167" s="6" t="n">
         <v>121.21</v>
       </c>
-      <c r="P167" s="7" t="n">
+      <c r="P167" s="6" t="n">
         <v>75</v>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -12629,10 +12598,10 @@
       <c r="L168" s="2" t="n"/>
       <c r="M168" s="2" t="n"/>
       <c r="N168" s="2" t="n"/>
-      <c r="O168" s="7" t="n">
+      <c r="O168" s="6" t="n">
         <v>375.5</v>
       </c>
-      <c r="P168" s="7" t="n">
+      <c r="P168" s="6" t="n">
         <v>270</v>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -12690,10 +12659,10 @@
         <v>8.5</v>
       </c>
       <c r="O169" s="9" t="n">
-        <v>405150.96</v>
+        <v>340871.73</v>
       </c>
       <c r="P169" s="9" t="n">
-        <v>240961.7</v>
+        <v>234136.7</v>
       </c>
       <c r="Q169" s="8" t="n"/>
       <c r="R169" s="8" t="n"/>
@@ -12779,7 +12748,7 @@
       <c r="C3" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -12788,7 +12757,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -12806,7 +12775,7 @@
       <c r="C4" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -12815,7 +12784,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -12833,7 +12802,7 @@
       <c r="C5" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -12842,7 +12811,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="6" t="n">
         <v>150</v>
       </c>
     </row>
@@ -12860,7 +12829,7 @@
       <c r="C6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -12869,7 +12838,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -12887,7 +12856,7 @@
       <c r="C7" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -12896,7 +12865,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="6" t="n">
         <v>75</v>
       </c>
     </row>
@@ -12914,7 +12883,7 @@
       <c r="C8" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -12923,7 +12892,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n"/>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="6" t="n">
         <v>75</v>
       </c>
     </row>
@@ -12941,7 +12910,7 @@
       <c r="C9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -12950,7 +12919,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n"/>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -12968,7 +12937,7 @@
       <c r="C10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -12977,7 +12946,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -12995,7 +12964,7 @@
       <c r="C11" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -13004,7 +12973,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n"/>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="6" t="n">
         <v>150</v>
       </c>
     </row>
@@ -13022,7 +12991,7 @@
       <c r="C12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -13031,7 +13000,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -13049,7 +13018,7 @@
       <c r="C13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -13058,7 +13027,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -13076,7 +13045,7 @@
       <c r="C14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -13085,7 +13054,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n"/>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="6" t="n">
         <v>200</v>
       </c>
     </row>
@@ -13103,7 +13072,7 @@
       <c r="C15" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -13112,7 +13081,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n"/>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="6" t="n">
         <v>75</v>
       </c>
     </row>
@@ -13130,7 +13099,7 @@
       <c r="C16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -13139,7 +13108,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n"/>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -13157,7 +13126,7 @@
       <c r="C17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -13166,7 +13135,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n"/>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -13184,7 +13153,7 @@
       <c r="C18" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -13193,7 +13162,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -13211,7 +13180,7 @@
       <c r="C19" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -13220,7 +13189,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -13238,7 +13207,7 @@
       <c r="C20" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -13247,7 +13216,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -13265,7 +13234,7 @@
       <c r="C21" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -13274,7 +13243,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="6" t="n">
         <v>75</v>
       </c>
     </row>
@@ -13292,7 +13261,7 @@
       <c r="C22" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -13301,7 +13270,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="6" t="n">
         <v>150</v>
       </c>
     </row>
@@ -13319,7 +13288,7 @@
       <c r="C23" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -13328,7 +13297,7 @@
         </is>
       </c>
       <c r="F23" s="2" t="n"/>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="6" t="n">
         <v>150</v>
       </c>
     </row>
@@ -13346,7 +13315,7 @@
       <c r="C24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -13355,7 +13324,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n"/>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -13373,7 +13342,7 @@
       <c r="C25" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13382,7 +13351,7 @@
         </is>
       </c>
       <c r="F25" s="2" t="n"/>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -13400,7 +13369,7 @@
       <c r="C26" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13409,7 +13378,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n"/>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -13427,7 +13396,7 @@
       <c r="C27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -13436,7 +13405,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n"/>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="6" t="n">
         <v>300</v>
       </c>
     </row>
@@ -13454,7 +13423,7 @@
       <c r="C28" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -13463,7 +13432,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n"/>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -13481,7 +13450,7 @@
       <c r="C29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -13490,7 +13459,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n"/>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="6" t="n">
         <v>200</v>
       </c>
     </row>
@@ -13508,7 +13477,7 @@
       <c r="C30" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -13517,7 +13486,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n"/>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="6" t="n">
         <v>150</v>
       </c>
     </row>
@@ -13535,7 +13504,7 @@
       <c r="C31" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -13544,7 +13513,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n"/>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -13562,7 +13531,7 @@
       <c r="C32" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -13571,7 +13540,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n"/>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="6" t="n">
         <v>150</v>
       </c>
     </row>
@@ -13589,7 +13558,7 @@
       <c r="C33" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -13598,7 +13567,7 @@
         </is>
       </c>
       <c r="F33" s="2" t="n"/>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -13616,7 +13585,7 @@
       <c r="C34" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -13625,7 +13594,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n"/>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="6" t="n">
         <v>125</v>
       </c>
     </row>
@@ -13643,7 +13612,7 @@
       <c r="C35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D35" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -13652,7 +13621,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n"/>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -13670,7 +13639,7 @@
       <c r="C36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -13679,7 +13648,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n"/>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="6" t="n">
         <v>200</v>
       </c>
     </row>
@@ -13697,7 +13666,7 @@
       <c r="C37" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D37" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -13706,7 +13675,7 @@
         </is>
       </c>
       <c r="F37" s="2" t="n"/>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="6" t="n">
         <v>800</v>
       </c>
     </row>
@@ -13724,7 +13693,7 @@
       <c r="C38" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -13733,7 +13702,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n"/>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -13751,7 +13720,7 @@
       <c r="C39" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="D39" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -13760,7 +13729,7 @@
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -13778,7 +13747,7 @@
       <c r="C40" s="2" t="n">
         <v>31.5</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -13787,7 +13756,7 @@
         </is>
       </c>
       <c r="F40" s="2" t="n"/>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="6" t="n">
         <v>3150</v>
       </c>
     </row>
@@ -13805,7 +13774,7 @@
       <c r="C41" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D41" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -13814,7 +13783,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n"/>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="6" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -13832,7 +13801,7 @@
       <c r="C42" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D42" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -13841,7 +13810,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
-      <c r="G42" s="7" t="n">
+      <c r="G42" s="6" t="n">
         <v>75</v>
       </c>
     </row>
@@ -13859,7 +13828,7 @@
       <c r="C43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="7" t="n">
+      <c r="D43" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -13868,7 +13837,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n"/>
-      <c r="G43" s="7" t="n">
+      <c r="G43" s="6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -13886,7 +13855,7 @@
       <c r="C44" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D44" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -13895,7 +13864,7 @@
         </is>
       </c>
       <c r="F44" s="2" t="n"/>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -13990,10 +13959,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14021,10 +13990,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14052,10 +14021,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F51" s="7" t="n">
+      <c r="F51" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G51" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14083,10 +14052,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F52" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G52" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14114,10 +14083,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14145,10 +14114,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F54" s="7" t="n">
+      <c r="F54" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="G54" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14176,10 +14145,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F55" s="7" t="n">
+      <c r="F55" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G55" s="7" t="n">
+      <c r="G55" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14207,10 +14176,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F56" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G56" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14238,10 +14207,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F57" s="7" t="n">
+      <c r="F57" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="G57" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14269,10 +14238,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F58" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="G58" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14300,10 +14269,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F59" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="G59" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14331,10 +14300,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F60" s="7" t="n">
+      <c r="F60" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G60" s="7" t="n">
+      <c r="G60" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14362,10 +14331,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F61" s="7" t="n">
+      <c r="F61" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G61" s="7" t="n">
+      <c r="G61" s="6" t="n">
         <v>200</v>
       </c>
     </row>
@@ -14393,10 +14362,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F62" s="7" t="n">
+      <c r="F62" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="G62" s="6" t="n">
         <v>200</v>
       </c>
     </row>
@@ -14424,10 +14393,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14455,10 +14424,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F64" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G64" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14486,10 +14455,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F65" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14517,10 +14486,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F66" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14548,10 +14517,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F67" s="7" t="n">
+      <c r="F67" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G67" s="7" t="n">
+      <c r="G67" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14579,10 +14548,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="G68" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14610,10 +14579,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F69" s="7" t="n">
+      <c r="F69" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G69" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14641,10 +14610,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F70" s="7" t="n">
+      <c r="F70" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G70" s="7" t="n">
+      <c r="G70" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14672,10 +14641,10 @@
           <t>rolls</t>
         </is>
       </c>
-      <c r="F71" s="7" t="n">
+      <c r="F71" s="6" t="n">
         <v>64.5</v>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="6" t="n">
         <v>2580</v>
       </c>
     </row>
@@ -14703,10 +14672,10 @@
           <t>rolls</t>
         </is>
       </c>
-      <c r="F72" s="7" t="n">
+      <c r="F72" s="6" t="n">
         <v>196</v>
       </c>
-      <c r="G72" s="7" t="n">
+      <c r="G72" s="6" t="n">
         <v>784</v>
       </c>
     </row>
@@ -14734,10 +14703,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F73" s="7" t="n">
+      <c r="F73" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G73" s="7" t="n">
+      <c r="G73" s="6" t="n">
         <v>400</v>
       </c>
     </row>
@@ -14765,10 +14734,10 @@
           <t>day</t>
         </is>
       </c>
-      <c r="F74" s="7" t="n">
+      <c r="F74" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G74" s="7" t="n">
+      <c r="G74" s="6" t="n">
         <v>400</v>
       </c>
     </row>
